--- a/open-world/config/excel/任务.xlsx
+++ b/open-world/config/excel/任务.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R19549e0cdd484745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="2" r:id="R1f10f921ea414c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务类型" sheetId="3" r:id="R055e11c222b84eb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="4" r:id="R626b9c679f9c4567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤" sheetId="5" r:id="R0df41b5364194086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线" sheetId="6" r:id="Rf49d5becd7e94a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件" sheetId="7" r:id="R00271037bd554825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="传闻" sheetId="8" r:id="R81d012e71eee472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能找回" sheetId="9" r:id="Ra4ec21f144ca4f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb384e06b98c844cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="2" r:id="Rd6f9310fd5f547da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务类型" sheetId="3" r:id="R648a6ef2f61447fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="4" r:id="Rcfb9dd9f6eaa419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤" sheetId="5" r:id="Rce88293f0a8246a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线" sheetId="6" r:id="R9bd6ca3db4bb4a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件" sheetId="7" r:id="R202ae1e0a74a403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="传闻" sheetId="8" r:id="R79aaad4a6ae94d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能找回" sheetId="9" r:id="Rbd709e079a2a4a43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1905,7 +1905,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d8060a21bdc4d27"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe9f7e8eda31480f"/>
 </x:worksheet>
 </file>
 
@@ -2317,7 +2317,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec600369b0a94df5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7437344fc7ab4e1a"/>
 </x:worksheet>
 </file>
 
@@ -2613,14 +2613,20 @@
           <x:t xml:space="preserve">裂星潮经验</x:t>
         </x:is>
       </x:c>
-      <x:c r="AV1" s="3" t="str">
-        <x:v>解锁海克斯槽</x:v>
-      </x:c>
-      <x:c r="AW1" s="3" t="str">
-        <x:v>海克斯选奖</x:v>
-      </x:c>
-      <x:c r="AX1" s="3" t="str">
-        <x:v>回响碎片奖励</x:v>
+      <x:c r="AV1" s="3"/>
+      <x:c r="AW1" s="3"/>
+      <x:c r="AX1" s="3"/>
+      <x:c r="AY1" t="str">
+        <x:v>frozen</x:v>
+      </x:c>
+      <x:c r="AZ1" t="str">
+        <x:v>hub_node</x:v>
+      </x:c>
+      <x:c r="BA1" t="str">
+        <x:v>hub_return</x:v>
+      </x:c>
+      <x:c r="BB1" t="str">
+        <x:v>hub_commission</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -2859,14 +2865,20 @@
           <x:t xml:space="preserve">reward_xp_hardmode</x:t>
         </x:is>
       </x:c>
-      <x:c r="AV2" s="4" t="str">
-        <x:v>reward_hex_slot</x:v>
-      </x:c>
-      <x:c r="AW2" s="4" t="str">
-        <x:v>reward_hex_choice</x:v>
-      </x:c>
-      <x:c r="AX2" s="4" t="str">
-        <x:v>reward_hex_shards</x:v>
+      <x:c r="AV2" s="4"/>
+      <x:c r="AW2" s="4"/>
+      <x:c r="AX2" s="4"/>
+      <x:c r="AY2" t="str">
+        <x:v>frozen</x:v>
+      </x:c>
+      <x:c r="AZ2" t="str">
+        <x:v>hub_node</x:v>
+      </x:c>
+      <x:c r="BA2" t="str">
+        <x:v>hub_return</x:v>
+      </x:c>
+      <x:c r="BB2" t="str">
+        <x:v>hub_commission</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3105,14 +3117,20 @@
           <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
-      <x:c r="AV3" s="4" t="str">
+      <x:c r="AV3" s="4"/>
+      <x:c r="AW3" s="4"/>
+      <x:c r="AX3" s="4"/>
+      <x:c r="AY3" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="AZ3" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="AW3" s="4" t="str">
-        <x:v>json</x:v>
-      </x:c>
-      <x:c r="AX3" s="4" t="str">
-        <x:v>int</x:v>
+      <x:c r="BA3" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="BB3" t="str">
+        <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3159,10 +3177,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="K4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J4"/>
+      <x:c r="K4" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="L4" t="inlineStr">
         <x:is>
@@ -3196,10 +3213,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T4" t="n">
-        <x:v>413</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U4" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V4" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W4" t="b">
         <x:v>0</x:v>
@@ -3231,6 +3251,9 @@
       <x:c r="AU4" t="n">
         <x:v>430</x:v>
       </x:c>
+      <x:c r="AZ4" t="str">
+        <x:v>wind-story-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
@@ -3276,11 +3299,7 @@
           <x:t xml:space="preserve">ss-npc-cheng</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c01-n01</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="J5"/>
       <x:c r="K5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">none</x:t>
@@ -3305,10 +3324,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T5" t="n">
-        <x:v>327</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U5" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V5" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W5" t="b">
         <x:v>0</x:v>
@@ -3340,6 +3362,9 @@
       <x:c r="AU5" t="n">
         <x:v>340</x:v>
       </x:c>
+      <x:c r="BA5" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
@@ -3385,15 +3410,9 @@
           <x:t xml:space="preserve">ss-npc-tongling</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c01-t02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J6"/>
+      <x:c r="K6" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="P6" t="inlineStr">
         <x:is>
@@ -3409,10 +3428,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T6" t="n">
-        <x:v>615</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U6" t="n">
-        <x:v>60</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W6" t="b">
         <x:v>0</x:v>
@@ -3444,6 +3466,9 @@
       <x:c r="AU6" t="n">
         <x:v>640</x:v>
       </x:c>
+      <x:c r="AZ6" t="str">
+        <x:v>wind-story-2</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
@@ -3489,10 +3514,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="K7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arrive</x:t>
-        </x:is>
+      <x:c r="J7"/>
+      <x:c r="K7" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="P7" t="inlineStr">
         <x:is>
@@ -3513,10 +3537,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T7" t="n">
-        <x:v>615</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U7" t="n">
-        <x:v>60</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V7" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W7" t="b">
         <x:v>0</x:v>
@@ -3553,6 +3580,9 @@
       <x:c r="AU7" t="n">
         <x:v>640</x:v>
       </x:c>
+      <x:c r="AZ7" t="str">
+        <x:v>wind-story-3</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
@@ -3598,10 +3628,9 @@
           <x:t xml:space="preserve">ss-npc-cheng</x:t>
         </x:is>
       </x:c>
-      <x:c r="K8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J8"/>
+      <x:c r="K8" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="P8" t="inlineStr">
         <x:is>
@@ -3622,10 +3651,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T8" t="n">
-        <x:v>1573</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U8" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W8" t="b">
         <x:v>0</x:v>
@@ -3662,6 +3694,9 @@
       <x:c r="AU8" t="n">
         <x:v>1070</x:v>
       </x:c>
+      <x:c r="AZ8" t="str">
+        <x:v>wind-gate</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
@@ -3707,6 +3742,7 @@
           <x:t xml:space="preserve">ss-npc-cheng</x:t>
         </x:is>
       </x:c>
+      <x:c r="J9"/>
       <x:c r="K9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">talk</x:t>
@@ -3726,10 +3762,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T9" t="n">
-        <x:v>1706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U9" t="n">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V9" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W9" t="b">
         <x:v>0</x:v>
@@ -3766,6 +3805,9 @@
       <x:c r="AU9" t="n">
         <x:v>1160</x:v>
       </x:c>
+      <x:c r="BA9" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
@@ -3811,10 +3853,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="K10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">discover</x:t>
-        </x:is>
+      <x:c r="J10"/>
+      <x:c r="K10" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="M10" t="inlineStr">
         <x:is>
@@ -3845,10 +3886,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T10" t="n">
-        <x:v>2232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U10" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V10" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W10" t="b">
         <x:v>0</x:v>
@@ -3885,6 +3929,9 @@
       <x:c r="AU10" t="n">
         <x:v>1386</x:v>
       </x:c>
+      <x:c r="AZ10" t="str">
+        <x:v>mist-story-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
@@ -3930,15 +3977,9 @@
           <x:t xml:space="preserve">ss-npc-qingmang</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c02-t01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J11"/>
+      <x:c r="K11" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="M11" t="inlineStr">
         <x:is>
@@ -3964,10 +4005,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T11" t="n">
-        <x:v>1780</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U11" t="n">
-        <x:v>90</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V11" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W11" t="b">
         <x:v>0</x:v>
@@ -4004,6 +4048,9 @@
       <x:c r="AU11" t="n">
         <x:v>1105</x:v>
       </x:c>
+      <x:c r="AZ11" t="str">
+        <x:v>mist-story-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="inlineStr">
@@ -4049,10 +4096,9 @@
           <x:t xml:space="preserve">ss-npc-qingmang</x:t>
         </x:is>
       </x:c>
-      <x:c r="K12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arrive</x:t>
-        </x:is>
+      <x:c r="J12"/>
+      <x:c r="K12" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="M12" t="inlineStr">
         <x:is>
@@ -4083,10 +4129,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T12" t="n">
-        <x:v>3341</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U12" t="n">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V12" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W12" t="b">
         <x:v>0</x:v>
@@ -4123,6 +4172,9 @@
       <x:c r="AU12" t="n">
         <x:v>2074</x:v>
       </x:c>
+      <x:c r="AZ12" t="str">
+        <x:v>mist-story-2</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="inlineStr">
@@ -4168,10 +4220,9 @@
           <x:t xml:space="preserve">ss-npc-qingmang</x:t>
         </x:is>
       </x:c>
-      <x:c r="K13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arrive</x:t>
-        </x:is>
+      <x:c r="J13"/>
+      <x:c r="K13" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="M13" t="inlineStr">
         <x:is>
@@ -4202,10 +4253,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T13" t="n">
-        <x:v>3341</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U13" t="n">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W13" t="b">
         <x:v>0</x:v>
@@ -4242,6 +4296,9 @@
       <x:c r="AU13" t="n">
         <x:v>2074</x:v>
       </x:c>
+      <x:c r="AZ13" t="str">
+        <x:v>mist-story-3</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="inlineStr">
@@ -4287,10 +4344,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J14"/>
+      <x:c r="K14" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="P14" t="inlineStr">
         <x:is>
@@ -4311,10 +4367,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T14" t="n">
-        <x:v>6121</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U14" t="n">
-        <x:v>400</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W14" t="b">
         <x:v>0</x:v>
@@ -4351,6 +4410,9 @@
       <x:c r="AU14" t="n">
         <x:v>3460</x:v>
       </x:c>
+      <x:c r="AZ14" t="str">
+        <x:v>mist-gate</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="inlineStr">
@@ -4396,6 +4458,7 @@
           <x:t xml:space="preserve">ss-npc-mijia</x:t>
         </x:is>
       </x:c>
+      <x:c r="J15"/>
       <x:c r="K15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">talk</x:t>
@@ -4415,10 +4478,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T15" t="n">
-        <x:v>6617</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U15" t="n">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V15" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W15" t="b">
         <x:v>0</x:v>
@@ -4455,6 +4521,9 @@
       <x:c r="AU15" t="n">
         <x:v>3740</x:v>
       </x:c>
+      <x:c r="BA15" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="inlineStr">
@@ -7231,10 +7300,8 @@
           <x:t xml:space="preserve">第一章 · 失踪的远行队</x:t>
         </x:is>
       </x:c>
-      <x:c r="G40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G40" t="str">
+        <x:v>找到被困的远行队，击破草原结界首领</x:v>
       </x:c>
       <x:c r="H40" t="inlineStr">
         <x:is>
@@ -7333,6 +7400,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY40" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="inlineStr">
@@ -7363,10 +7433,8 @@
           <x:t xml:space="preserve">第二章 · 被修改的路标</x:t>
         </x:is>
       </x:c>
-      <x:c r="G41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G41" t="str">
+        <x:v>追查被篡改的路标，击破林中结界首领</x:v>
       </x:c>
       <x:c r="H41" t="inlineStr">
         <x:is>
@@ -7470,6 +7538,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY41" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="inlineStr">
@@ -7500,10 +7571,8 @@
           <x:t xml:space="preserve">第三章 · 熄灭的炉火</x:t>
         </x:is>
       </x:c>
-      <x:c r="G42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G42" t="str">
+        <x:v>重燃熄灭的炉火，击破守炉的结界首领</x:v>
       </x:c>
       <x:c r="H42" t="inlineStr">
         <x:is>
@@ -7607,6 +7676,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY42" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="inlineStr">
@@ -7637,10 +7709,8 @@
           <x:t xml:space="preserve">第四章 · 冰下的求救声</x:t>
         </x:is>
       </x:c>
-      <x:c r="G43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G43" t="str">
+        <x:v>循着冰下的求救声，击破冰原结界首领</x:v>
       </x:c>
       <x:c r="H43" t="inlineStr">
         <x:is>
@@ -7744,6 +7814,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY43" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="inlineStr">
@@ -7774,10 +7847,8 @@
           <x:t xml:space="preserve">第五章 · 没有归来的人</x:t>
         </x:is>
       </x:c>
-      <x:c r="G44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G44" t="str">
+        <x:v>找回没有归来的人，击破深渊结界首领</x:v>
       </x:c>
       <x:c r="H44" t="inlineStr">
         <x:is>
@@ -7881,6 +7952,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY44" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="inlineStr">
@@ -7911,10 +7985,8 @@
           <x:t xml:space="preserve">第六章 · 最后一条归途</x:t>
         </x:is>
       </x:c>
-      <x:c r="G45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">完成救援并突破首领结界</x:t>
-        </x:is>
+      <x:c r="G45" t="str">
+        <x:v>打通最后一条归途，击破龙骨结界首领</x:v>
       </x:c>
       <x:c r="H45" t="inlineStr">
         <x:is>
@@ -8018,6 +8090,9 @@
           <x:t xml:space="preserve">挑战首领结界</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY45" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="inlineStr">
@@ -8104,6 +8179,9 @@
           <x:t xml:space="preserve">目标已达成，领取奖励后收入档案。</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY46" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="inlineStr">
@@ -8192,6 +8270,9 @@
           <x:t xml:space="preserve">目标已达成，领取奖励后收入档案。</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY47" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="inlineStr">
@@ -8274,6 +8355,9 @@
           <x:t xml:space="preserve">m0-wind-z1-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY48" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="inlineStr">
@@ -8354,6 +8438,9 @@
           <x:t xml:space="preserve">m0-wind-z1-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY49" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="inlineStr">
@@ -8431,6 +8518,9 @@
           <x:t xml:space="preserve">m0-wind-z1-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY50" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="inlineStr">
@@ -8513,6 +8603,9 @@
           <x:t xml:space="preserve">m0-wind-z2-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY51" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="inlineStr">
@@ -8593,6 +8686,9 @@
           <x:t xml:space="preserve">m0-wind-z2-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY52" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="inlineStr">
@@ -8670,6 +8766,9 @@
           <x:t xml:space="preserve">m0-wind-z2-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY53" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="inlineStr">
@@ -8752,6 +8851,9 @@
           <x:t xml:space="preserve">m0-wind-z3-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY54" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="inlineStr">
@@ -8832,6 +8934,9 @@
           <x:t xml:space="preserve">m0-wind-z3-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY55" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="inlineStr">
@@ -8909,6 +9014,9 @@
           <x:t xml:space="preserve">m0-wind-z3-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY56" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="inlineStr">
@@ -8991,6 +9099,9 @@
           <x:t xml:space="preserve">m0-wind-z4-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY57" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="inlineStr">
@@ -9071,6 +9182,9 @@
           <x:t xml:space="preserve">m0-wind-z4-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY58" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="inlineStr">
@@ -9148,6 +9262,9 @@
           <x:t xml:space="preserve">m0-wind-z4-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY59" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="inlineStr">
@@ -9230,6 +9347,9 @@
           <x:t xml:space="preserve">m0-wind-z5-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY60" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="inlineStr">
@@ -9310,6 +9430,9 @@
           <x:t xml:space="preserve">m0-wind-z5-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY61" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="inlineStr">
@@ -9387,6 +9510,9 @@
           <x:t xml:space="preserve">m0-wind-z5-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY62" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="inlineStr">
@@ -9469,6 +9595,9 @@
           <x:t xml:space="preserve">m0-wind-z6-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY63" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="inlineStr">
@@ -9549,6 +9678,9 @@
           <x:t xml:space="preserve">m0-wind-z6-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY64" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="inlineStr">
@@ -9626,6 +9758,9 @@
           <x:t xml:space="preserve">m0-wind-z6-bounty</x:t>
         </x:is>
       </x:c>
+      <x:c r="AY65" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="inlineStr">
@@ -9644,42 +9779,30 @@
         </x:is>
       </x:c>
       <x:c r="D66" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E66" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">guide</x:t>
         </x:is>
       </x:c>
-      <x:c r="F66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟上米洛</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟着米洛到船台湾，触碰航标并听他介绍前哨。</x:t>
-        </x:is>
+      <x:c r="F66" t="str">
+        <x:v>星门教学</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>去港口中央的星门</x:v>
       </x:c>
       <x:c r="I66" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="J66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c01-t01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c01-n01:accept</x:t>
-        </x:is>
+      <x:c r="J66"/>
+      <x:c r="K66" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="P66" t="str">
+        <x:v>hub:stargate:1</x:v>
       </x:c>
       <x:c r="Q66" t="inlineStr">
         <x:is>
@@ -9705,10 +9828,8 @@
           <x:t xml:space="preserve">岛屿故事</x:t>
         </x:is>
       </x:c>
-      <x:c r="AL66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">onboarding</x:t>
-        </x:is>
+      <x:c r="AL66" t="str">
+        <x:v>onboarding</x:v>
       </x:c>
       <x:c r="AO66" t="inlineStr">
         <x:is>
@@ -9723,7 +9844,7 @@
       <x:c r="AQ66" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AR66" t="b">
+      <x:c r="AR66" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -9766,10 +9887,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="K67" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">discover</x:t>
-        </x:is>
+      <x:c r="J67"/>
+      <x:c r="K67" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="P67" t="inlineStr">
         <x:is>
@@ -9787,10 +9907,13 @@
         </x:is>
       </x:c>
       <x:c r="T67" t="n">
-        <x:v>464</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U67" t="n">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V67" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W67" t="b">
         <x:v>1</x:v>
@@ -9826,6 +9949,9 @@
       <x:c r="AR67" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AZ67" t="str">
+        <x:v>wind-story-2</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="inlineStr">
@@ -9856,10 +9982,8 @@
           <x:t xml:space="preserve">找回羊群的铃铛</x:t>
         </x:is>
       </x:c>
-      <x:c r="G68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉草坡上的营地，找回被巡猎兽叼走的羊铃。</x:t>
-        </x:is>
+      <x:c r="G68" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I68" t="inlineStr">
         <x:is>
@@ -9876,40 +10000,39 @@
           <x:t xml:space="preserve">ow-npc-wind-1</x:t>
         </x:is>
       </x:c>
-      <x:c r="M68" t="inlineStr">
+      <x:c r="M68" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z1-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z1-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W68" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD68" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z1-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z1-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T68" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U68" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="W68" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE68" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">落风坡</x:t>
@@ -9937,6 +10060,9 @@
       </x:c>
       <x:c r="AQ68" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ68" t="str">
+        <x:v>wind-nest-1</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -9968,10 +10094,8 @@
           <x:t xml:space="preserve">查清草坡足迹</x:t>
         </x:is>
       </x:c>
-      <x:c r="G69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">查看草坡上夜里留下的陌生脚印。</x:t>
-        </x:is>
+      <x:c r="G69" t="str">
+        <x:v>通关 风栖 · 沉船货舱。</x:v>
       </x:c>
       <x:c r="I69" t="inlineStr">
         <x:is>
@@ -9988,40 +10112,39 @@
           <x:t xml:space="preserve">ow-npc-wind-1</x:t>
         </x:is>
       </x:c>
-      <x:c r="M69" t="inlineStr">
+      <x:c r="M69" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P69" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z1-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R69" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z1-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W69" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD69" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z1-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z1-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T69" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U69" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="W69" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE69" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">落风坡</x:t>
@@ -10049,6 +10172,9 @@
       </x:c>
       <x:c r="AQ69" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ69" t="str">
+        <x:v>wind-nest-2</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -10132,6 +10258,9 @@
       <x:c r="AQ70" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY70" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="inlineStr">
@@ -10156,7 +10285,7 @@
         <x:v>稳住落风坡</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>赶走落风坡上游荡的 8 只怪物</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K71" t="inlineStr">
         <x:is>
@@ -10167,7 +10296,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U71" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Y71" t="inlineStr">
         <x:is>
@@ -10219,7 +10348,7 @@
         <x:v>坡头的头目</x:v>
       </x:c>
       <x:c r="G72" t="str">
-        <x:v>击败占住坡头的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K72" t="inlineStr">
         <x:is>
@@ -10282,7 +10411,7 @@
         <x:v>清出下坡路</x:v>
       </x:c>
       <x:c r="G73" t="str">
-        <x:v>清掉落风坡通往船台的 15 只拦路者</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K73" t="inlineStr">
         <x:is>
@@ -10351,10 +10480,8 @@
           <x:t xml:space="preserve">抢修小艇</x:t>
         </x:is>
       </x:c>
-      <x:c r="G74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">稳住小艇引擎，守住修船现场，击退3名侵军。</x:t>
-        </x:is>
+      <x:c r="G74" t="str">
+        <x:v>通关 风栖 · 风车旧井。</x:v>
       </x:c>
       <x:c r="I74" t="inlineStr">
         <x:is>
@@ -10371,40 +10498,39 @@
           <x:t xml:space="preserve">ow-npc-wind-2</x:t>
         </x:is>
       </x:c>
-      <x:c r="M74" t="inlineStr">
+      <x:c r="M74" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N74" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z2-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z2-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W74" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD74" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z2-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z2-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T74" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U74" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="W74" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE74" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">船台湾</x:t>
@@ -10432,6 +10558,9 @@
       </x:c>
       <x:c r="AQ74" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ74" t="str">
+        <x:v>wind-hunt</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -10463,10 +10592,8 @@
           <x:t xml:space="preserve">找回修船工具</x:t>
         </x:is>
       </x:c>
-      <x:c r="G75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">在船台湾的货堆里找回老戈的扳手和卡钳。</x:t>
-        </x:is>
+      <x:c r="G75" t="str">
+        <x:v>通关 风栖 · 风车地宫。</x:v>
       </x:c>
       <x:c r="I75" t="inlineStr">
         <x:is>
@@ -10483,40 +10610,39 @@
           <x:t xml:space="preserve">ow-npc-wind-2</x:t>
         </x:is>
       </x:c>
-      <x:c r="M75" t="inlineStr">
+      <x:c r="M75" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N75" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P75" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z2-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R75" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z2-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W75" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD75" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z2-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z2-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T75" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U75" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="W75" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE75" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">船台湾</x:t>
@@ -10544,6 +10670,9 @@
       </x:c>
       <x:c r="AQ75" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ75" t="str">
+        <x:v>wind-tide</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -10627,6 +10756,9 @@
       <x:c r="AQ76" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY76" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="inlineStr">
@@ -10651,7 +10783,7 @@
         <x:v>夺回船台外围</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>把船台湾外围的 8 只侵军散兵赶走</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K77" t="inlineStr">
         <x:is>
@@ -10662,7 +10794,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U77" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Y77" t="inlineStr">
         <x:is>
@@ -10714,7 +10846,7 @@
         <x:v>看守引擎的精英</x:v>
       </x:c>
       <x:c r="G78" t="str">
-        <x:v>击败守在船台引擎旁的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K78" t="inlineStr">
         <x:is>
@@ -10777,7 +10909,7 @@
         <x:v>保住船台后路</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>肃清船台湾四周的 15 只敌人，保住撤退路线</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K79" t="inlineStr">
         <x:is>
@@ -10846,10 +10978,8 @@
           <x:t xml:space="preserve">找回风向布</x:t>
         </x:is>
       </x:c>
-      <x:c r="G80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉风车高地的营地，顺着架台痕迹找回被偷的风向布。</x:t>
-        </x:is>
+      <x:c r="G80" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I80" t="inlineStr">
         <x:is>
@@ -10866,40 +10996,39 @@
           <x:t xml:space="preserve">ow-npc-wind-3</x:t>
         </x:is>
       </x:c>
-      <x:c r="M80" t="inlineStr">
+      <x:c r="M80" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N80" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z3-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z3-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W80" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD80" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z3-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z3-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T80" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U80" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="W80" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE80" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">风车高地</x:t>
@@ -10926,6 +11055,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ80" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY80" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ80" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB80" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -10958,10 +11096,8 @@
           <x:t xml:space="preserve">抄下那天的风向</x:t>
         </x:is>
       </x:c>
-      <x:c r="G81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">抄下光落下那天风车上刻的风向记录。</x:t>
-        </x:is>
+      <x:c r="G81" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I81" t="inlineStr">
         <x:is>
@@ -10978,40 +11114,39 @@
           <x:t xml:space="preserve">ow-npc-wind-3</x:t>
         </x:is>
       </x:c>
-      <x:c r="M81" t="inlineStr">
+      <x:c r="M81" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N81" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P81" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z3-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R81" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z3-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W81" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD81" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z3-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z3-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T81" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U81" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="W81" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE81" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">风车高地</x:t>
@@ -11038,6 +11173,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ81" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY81" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ81" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB81" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -11122,6 +11266,9 @@
       <x:c r="AQ82" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY82" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="inlineStr">
@@ -11146,7 +11293,7 @@
         <x:v>风车脚下</x:v>
       </x:c>
       <x:c r="G83" t="str">
-        <x:v>清掉风车高地上乱窜的 8 只怪物</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K83" t="inlineStr">
         <x:is>
@@ -11157,7 +11304,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U83" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Y83" t="inlineStr">
         <x:is>
@@ -11209,7 +11356,7 @@
         <x:v>高地上的猎手</x:v>
       </x:c>
       <x:c r="G84" t="str">
-        <x:v>击败在风车高地游猎的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K84" t="inlineStr">
         <x:is>
@@ -11272,7 +11419,7 @@
         <x:v>让风车重新转起来</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>肃清风车高地的 15 只敌人，让风吹过叶片</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K85" t="inlineStr">
         <x:is>
@@ -11341,10 +11488,8 @@
           <x:t xml:space="preserve">被逼入伙的拾荒者</x:t>
         </x:is>
       </x:c>
-      <x:c r="G86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉旧码头的营地，找到只想带家人离开的拾荒者。</x:t>
-        </x:is>
+      <x:c r="G86" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I86" t="inlineStr">
         <x:is>
@@ -11361,40 +11506,39 @@
           <x:t xml:space="preserve">ow-npc-wind-4</x:t>
         </x:is>
       </x:c>
-      <x:c r="M86" t="inlineStr">
+      <x:c r="M86" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N86" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P86" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z4-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R86" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z4-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T86" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U86" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V86" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD86" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z4-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z4-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T86" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U86" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="W86" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE86" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">旧码头</x:t>
@@ -11421,6 +11565,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY86" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ86" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB86" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -11453,10 +11606,8 @@
           <x:t xml:space="preserve">找回码头的粮食</x:t>
         </x:is>
       </x:c>
-      <x:c r="G87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">翻找星钩头目抢来的货堆，把粮食找回来。</x:t>
-        </x:is>
+      <x:c r="G87" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I87" t="inlineStr">
         <x:is>
@@ -11473,40 +11624,39 @@
           <x:t xml:space="preserve">ow-npc-wind-4</x:t>
         </x:is>
       </x:c>
-      <x:c r="M87" t="inlineStr">
+      <x:c r="M87" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N87" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P87" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z4-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R87" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z4-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T87" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U87" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V87" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W87" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD87" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z4-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z4-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T87" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U87" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="W87" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE87" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">旧码头</x:t>
@@ -11533,6 +11683,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ87" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY87" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ87" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB87" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -11617,6 +11776,9 @@
       <x:c r="AQ88" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY88" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="inlineStr">
@@ -11641,7 +11803,7 @@
         <x:v>码头清场</x:v>
       </x:c>
       <x:c r="G89" t="str">
-        <x:v>赶走旧码头栈桥上的 8 只怪物</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K89" t="inlineStr">
         <x:is>
@@ -11652,7 +11814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U89" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Y89" t="inlineStr">
         <x:is>
@@ -11704,7 +11866,7 @@
         <x:v>栈桥守卫</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>击败把守旧码头栈桥的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K90" t="inlineStr">
         <x:is>
@@ -11767,7 +11929,7 @@
         <x:v>打通便道</x:v>
       </x:c>
       <x:c r="G91" t="str">
-        <x:v>肃清旧码头到岸线之间的 15 只敌人</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K91" t="inlineStr">
         <x:is>
@@ -11836,10 +11998,8 @@
           <x:t xml:space="preserve">重新点亮岸线灯塔</x:t>
         </x:is>
       </x:c>
-      <x:c r="G92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉灯塔下的营地，核对灯塔记录，让灯塔重新点亮。</x:t>
-        </x:is>
+      <x:c r="G92" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I92" t="inlineStr">
         <x:is>
@@ -11856,40 +12016,39 @@
           <x:t xml:space="preserve">ow-npc-wind-5</x:t>
         </x:is>
       </x:c>
-      <x:c r="M92" t="inlineStr">
+      <x:c r="M92" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N92" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P92" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z5-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R92" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z5-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W92" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD92" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z5-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z5-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T92" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U92" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="W92" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE92" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">岸线崖</x:t>
@@ -11916,6 +12075,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ92" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY92" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ92" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB92" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -11948,10 +12116,8 @@
           <x:t xml:space="preserve">核对岸线标记</x:t>
         </x:is>
       </x:c>
-      <x:c r="G93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">把岸线崖上被挪过的标记核对归位。</x:t>
-        </x:is>
+      <x:c r="G93" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I93" t="inlineStr">
         <x:is>
@@ -11968,40 +12134,39 @@
           <x:t xml:space="preserve">ow-npc-wind-5</x:t>
         </x:is>
       </x:c>
-      <x:c r="M93" t="inlineStr">
+      <x:c r="M93" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N93" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P93" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z5-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R93" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z5-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W93" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD93" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z5-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z5-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T93" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U93" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="W93" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE93" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">岸线崖</x:t>
@@ -12028,6 +12193,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ93" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY93" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ93" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB93" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -12112,6 +12286,9 @@
       <x:c r="AQ94" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY94" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="inlineStr">
@@ -12136,7 +12313,7 @@
         <x:v>崖边游荡者</x:v>
       </x:c>
       <x:c r="G95" t="str">
-        <x:v>清掉岸线崖小径上的 8 只怪物</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K95" t="inlineStr">
         <x:is>
@@ -12147,7 +12324,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U95" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Y95" t="inlineStr">
         <x:is>
@@ -12199,7 +12376,7 @@
         <x:v>崖顶看守</x:v>
       </x:c>
       <x:c r="G96" t="str">
-        <x:v>击败占据岸线崖顶的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K96" t="inlineStr">
         <x:is>
@@ -12210,7 +12387,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U96" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y96" t="inlineStr">
         <x:is>
@@ -12262,7 +12439,7 @@
         <x:v>守住崖路</x:v>
       </x:c>
       <x:c r="G97" t="str">
-        <x:v>肃清岸线崖沿路的 15 只敌人，护住崖路</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K97" t="inlineStr">
         <x:is>
@@ -12273,7 +12450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U97" t="n">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y97" t="inlineStr">
         <x:is>
@@ -12331,10 +12508,8 @@
           <x:t xml:space="preserve">没有寄出的家书</x:t>
         </x:is>
       </x:c>
-      <x:c r="G98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉要塞外的营地，找回莱恩没寄出的家书。</x:t>
-        </x:is>
+      <x:c r="G98" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I98" t="inlineStr">
         <x:is>
@@ -12351,40 +12526,39 @@
           <x:t xml:space="preserve">ow-npc-wind-6</x:t>
         </x:is>
       </x:c>
-      <x:c r="M98" t="inlineStr">
+      <x:c r="M98" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N98" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P98" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z6-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R98" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z6-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W98" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD98" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z6-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z6-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T98" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U98" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W98" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE98" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">船坞要塞</x:t>
@@ -12411,6 +12585,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ98" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY98" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ98" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB98" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -12443,10 +12626,8 @@
           <x:t xml:space="preserve">送达逃兵口信</x:t>
         </x:is>
       </x:c>
-      <x:c r="G99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">把莱恩的口信带到要塞墙下，让想走的兵看见。</x:t>
-        </x:is>
+      <x:c r="G99" t="str">
+        <x:v>通关 风栖 · 风车地窖。</x:v>
       </x:c>
       <x:c r="I99" t="inlineStr">
         <x:is>
@@ -12463,40 +12644,39 @@
           <x:t xml:space="preserve">ow-npc-wind-6</x:t>
         </x:is>
       </x:c>
-      <x:c r="M99" t="inlineStr">
+      <x:c r="M99" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N99" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P99" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z6-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R99" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-wind-side-z6-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W99" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD99" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-wind</x:t>
         </x:is>
       </x:c>
-      <x:c r="N99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-resident6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z6-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-side-z6-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T99" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="U99" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W99" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE99" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">船坞要塞</x:t>
@@ -12523,6 +12703,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ99" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY99" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ99" t="str">
+        <x:v>wind-nest-1</x:v>
+      </x:c>
+      <x:c r="BB99" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -12607,6 +12796,9 @@
       <x:c r="AQ100" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY100" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="inlineStr">
@@ -12631,7 +12823,7 @@
         <x:v>要塞外墙</x:v>
       </x:c>
       <x:c r="G101" t="str">
-        <x:v>击退船坞要塞外墙下的 8 只怪物</x:v>
+        <x:v>在风栖任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K101" t="inlineStr">
         <x:is>
@@ -12642,7 +12834,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U101" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Y101" t="inlineStr">
         <x:is>
@@ -12694,7 +12886,7 @@
         <x:v>要塞百夫长</x:v>
       </x:c>
       <x:c r="G102" t="str">
-        <x:v>击败镇守船坞要塞的 1 只精英</x:v>
+        <x:v>在风栖任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K102" t="inlineStr">
         <x:is>
@@ -12705,7 +12897,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U102" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y102" t="inlineStr">
         <x:is>
@@ -12757,7 +12949,7 @@
         <x:v>削弱要塞守军</x:v>
       </x:c>
       <x:c r="G103" t="str">
-        <x:v>消灭船坞要塞内外的 15 名守军，削弱防线</x:v>
+        <x:v>在风栖任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K103" t="inlineStr">
         <x:is>
@@ -12768,7 +12960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U103" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Y103" t="inlineStr">
         <x:is>
@@ -12893,6 +13085,9 @@
       <x:c r="AQ104" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY104" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="inlineStr">
@@ -12990,6 +13185,9 @@
       <x:c r="AQ105" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY105" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="inlineStr">
@@ -13087,6 +13285,9 @@
       <x:c r="AQ106" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY106" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="inlineStr">
@@ -13197,6 +13398,9 @@
       <x:c r="AU107" t="n">
         <x:v>813</x:v>
       </x:c>
+      <x:c r="AY107" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="inlineStr">
@@ -13237,15 +13441,9 @@
           <x:t xml:space="preserve">ss-npc-qingmang</x:t>
         </x:is>
       </x:c>
-      <x:c r="J108" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c02-t03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K108" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J108"/>
+      <x:c r="K108" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="L108" t="inlineStr">
         <x:is>
@@ -13273,10 +13471,13 @@
         </x:is>
       </x:c>
       <x:c r="T108" t="n">
-        <x:v>1378</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U108" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V108" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W108" t="b">
         <x:v>1</x:v>
@@ -13312,6 +13513,9 @@
       <x:c r="AU108" t="n">
         <x:v>813</x:v>
       </x:c>
+      <x:c r="AZ108" t="str">
+        <x:v>mist-story-2</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="inlineStr">
@@ -13352,15 +13556,9 @@
           <x:t xml:space="preserve">ss-npc-milo</x:t>
         </x:is>
       </x:c>
-      <x:c r="J109" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-c02-t04</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K109" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">none</x:t>
-        </x:is>
+      <x:c r="J109"/>
+      <x:c r="K109" t="str">
+        <x:v>none</x:v>
       </x:c>
       <x:c r="L109" t="inlineStr">
         <x:is>
@@ -13388,10 +13586,13 @@
         </x:is>
       </x:c>
       <x:c r="T109" t="n">
-        <x:v>1378</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U109" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V109" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W109" t="b">
         <x:v>1</x:v>
@@ -13427,6 +13628,9 @@
       <x:c r="AU109" t="n">
         <x:v>815</x:v>
       </x:c>
+      <x:c r="AZ109" t="str">
+        <x:v>mist-story-3</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="inlineStr">
@@ -13457,10 +13661,8 @@
           <x:t xml:space="preserve">找回迷航渡船的铃</x:t>
         </x:is>
       </x:c>
-      <x:c r="G110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉林子边的营地，找回被拖走的渡船铃。</x:t>
-        </x:is>
+      <x:c r="G110" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I110" t="inlineStr">
         <x:is>
@@ -13477,40 +13679,39 @@
           <x:t xml:space="preserve">ow-npc-mist-1</x:t>
         </x:is>
       </x:c>
-      <x:c r="M110" t="inlineStr">
+      <x:c r="M110" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N110" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P110" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z1-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R110" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z1-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W110" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD110" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z1-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z1-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T110" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U110" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="W110" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE110" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">雾铃渡口</x:t>
@@ -13538,6 +13739,9 @@
       </x:c>
       <x:c r="AQ110" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ110" t="str">
+        <x:v>mist-nest-1</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -13569,10 +13773,8 @@
           <x:t xml:space="preserve">渡口的潮汐牌</x:t>
         </x:is>
       </x:c>
-      <x:c r="G111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">查看渡口潮汐牌上最后一条出入记录。</x:t>
-        </x:is>
+      <x:c r="G111" t="str">
+        <x:v>通关 雾铃 · 废弃邮站。</x:v>
       </x:c>
       <x:c r="I111" t="inlineStr">
         <x:is>
@@ -13589,40 +13791,39 @@
           <x:t xml:space="preserve">ow-npc-mist-1</x:t>
         </x:is>
       </x:c>
-      <x:c r="M111" t="inlineStr">
+      <x:c r="M111" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N111" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P111" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z1-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R111" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z1-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W111" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD111" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z1-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z1-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T111" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U111" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="W111" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE111" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">雾铃渡口</x:t>
@@ -13650,6 +13851,9 @@
       </x:c>
       <x:c r="AQ111" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ111" t="str">
+        <x:v>mist-nest-2</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -13733,6 +13937,9 @@
       <x:c r="AQ112" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY112" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="inlineStr">
@@ -13757,7 +13964,7 @@
         <x:v>渡口驱雾</x:v>
       </x:c>
       <x:c r="G113" t="str">
-        <x:v>驱散雾铃渡口浓雾里的 8 只怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K113" t="inlineStr">
         <x:is>
@@ -13768,7 +13975,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U113" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y113" t="inlineStr">
         <x:is>
@@ -13820,7 +14027,7 @@
         <x:v>渡口监工</x:v>
       </x:c>
       <x:c r="G114" t="str">
-        <x:v>击败看守渡口货栈的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K114" t="inlineStr">
         <x:is>
@@ -13831,7 +14038,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U114" t="n">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y114" t="inlineStr">
         <x:is>
@@ -13883,7 +14090,7 @@
         <x:v>货栈周边</x:v>
       </x:c>
       <x:c r="G115" t="str">
-        <x:v>肃清雾铃渡口货栈周边的 15 只敌人</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K115" t="inlineStr">
         <x:is>
@@ -13894,7 +14101,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U115" t="n">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Y115" t="inlineStr">
         <x:is>
@@ -13952,10 +14159,8 @@
           <x:t xml:space="preserve">抢回失落的邮包</x:t>
         </x:is>
       </x:c>
-      <x:c r="G116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉林道边翻邮包的营地，把豆丁的邮包抢回来。</x:t>
-        </x:is>
+      <x:c r="G116" t="str">
+        <x:v>通关 雾铃 · 树穴深处。</x:v>
       </x:c>
       <x:c r="I116" t="inlineStr">
         <x:is>
@@ -13972,40 +14177,39 @@
           <x:t xml:space="preserve">ow-npc-mist-2</x:t>
         </x:is>
       </x:c>
-      <x:c r="M116" t="inlineStr">
+      <x:c r="M116" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z2-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z2-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W116" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD116" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z2-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z2-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T116" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U116" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="W116" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE116" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">邮路林道</x:t>
@@ -14033,6 +14237,9 @@
       </x:c>
       <x:c r="AQ116" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ116" t="str">
+        <x:v>mist-hunt</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -14064,10 +14271,8 @@
           <x:t xml:space="preserve">林道路牌的记号</x:t>
         </x:is>
       </x:c>
-      <x:c r="G117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">抄下林道路牌上邮差留的记号。</x:t>
-        </x:is>
+      <x:c r="G117" t="str">
+        <x:v>通关 雾铃 · 邮站前庭。</x:v>
       </x:c>
       <x:c r="I117" t="inlineStr">
         <x:is>
@@ -14084,40 +14289,39 @@
           <x:t xml:space="preserve">ow-npc-mist-2</x:t>
         </x:is>
       </x:c>
-      <x:c r="M117" t="inlineStr">
+      <x:c r="M117" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z2-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z2-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W117" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD117" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z2-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z2-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T117" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U117" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="W117" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE117" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">邮路林道</x:t>
@@ -14145,6 +14349,9 @@
       </x:c>
       <x:c r="AQ117" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ117" t="str">
+        <x:v>mist-tide</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -14228,6 +14435,9 @@
       <x:c r="AQ118" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY118" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="inlineStr">
@@ -14252,7 +14462,7 @@
         <x:v>林道拦路者</x:v>
       </x:c>
       <x:c r="G119" t="str">
-        <x:v>清掉邮路林道上拦信的 8 只怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K119" t="inlineStr">
         <x:is>
@@ -14263,7 +14473,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U119" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y119" t="inlineStr">
         <x:is>
@@ -14315,7 +14525,7 @@
         <x:v>截信的头目</x:v>
       </x:c>
       <x:c r="G120" t="str">
-        <x:v>击败在邮路林道截信的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K120" t="inlineStr">
         <x:is>
@@ -14326,7 +14536,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U120" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y120" t="inlineStr">
         <x:is>
@@ -14378,7 +14588,7 @@
         <x:v>恢复邮路</x:v>
       </x:c>
       <x:c r="G121" t="str">
-        <x:v>肃清邮路林道沿线的 15 只敌人，让信使能走</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K121" t="inlineStr">
         <x:is>
@@ -14389,7 +14599,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U121" t="n">
-        <x:v>60</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y121" t="inlineStr">
         <x:is>
@@ -14447,10 +14657,8 @@
           <x:t xml:space="preserve">找回邮站暗号板</x:t>
         </x:is>
       </x:c>
-      <x:c r="G122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉谷里的营地，找回被人冒用的暗号板。</x:t>
-        </x:is>
+      <x:c r="G122" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I122" t="inlineStr">
         <x:is>
@@ -14467,40 +14675,39 @@
           <x:t xml:space="preserve">ow-npc-mist-3</x:t>
         </x:is>
       </x:c>
-      <x:c r="M122" t="inlineStr">
+      <x:c r="M122" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N122" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P122" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z3-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R122" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z3-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W122" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD122" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z3-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z3-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T122" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U122" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="W122" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE122" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">三邮站谷</x:t>
@@ -14527,6 +14734,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ122" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY122" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ122" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB122" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -14559,10 +14775,8 @@
           <x:t xml:space="preserve">三站交接簿</x:t>
         </x:is>
       </x:c>
-      <x:c r="G123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">核对姜伯收齐的三站交接簿，对一对时间。</x:t>
-        </x:is>
+      <x:c r="G123" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I123" t="inlineStr">
         <x:is>
@@ -14579,40 +14793,39 @@
           <x:t xml:space="preserve">ow-npc-mist-3</x:t>
         </x:is>
       </x:c>
-      <x:c r="M123" t="inlineStr">
+      <x:c r="M123" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N123" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P123" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z3-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R123" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z3-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W123" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD123" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z3-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z3-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T123" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U123" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="W123" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE123" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">三邮站谷</x:t>
@@ -14639,6 +14852,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ123" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY123" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ123" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB123" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -14723,6 +14945,9 @@
       <x:c r="AQ124" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY124" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="inlineStr">
@@ -14747,7 +14972,7 @@
         <x:v>邮站外围</x:v>
       </x:c>
       <x:c r="G125" t="str">
-        <x:v>赶走三邮站谷邮站旧址旁的 8 只怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K125" t="inlineStr">
         <x:is>
@@ -14758,7 +14983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U125" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y125" t="inlineStr">
         <x:is>
@@ -14810,7 +15035,7 @@
         <x:v>织网的猎手</x:v>
       </x:c>
       <x:c r="G126" t="str">
-        <x:v>击败盘踞邮站谷的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K126" t="inlineStr">
         <x:is>
@@ -14821,7 +15046,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U126" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y126" t="inlineStr">
         <x:is>
@@ -14873,7 +15098,7 @@
         <x:v>清理邮站谷</x:v>
       </x:c>
       <x:c r="G127" t="str">
-        <x:v>肃清三邮站谷的 15 只敌人，保住三座邮站</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K127" t="inlineStr">
         <x:is>
@@ -14884,7 +15109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U127" t="n">
-        <x:v>60</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Y127" t="inlineStr">
         <x:is>
@@ -14942,10 +15167,8 @@
           <x:t xml:space="preserve">清除织网者巢穴</x:t>
         </x:is>
       </x:c>
-      <x:c r="G128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉树冠上的营地，拆掉织网者的巢。</x:t>
-        </x:is>
+      <x:c r="G128" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I128" t="inlineStr">
         <x:is>
@@ -14962,40 +15185,39 @@
           <x:t xml:space="preserve">ow-npc-mist-4</x:t>
         </x:is>
       </x:c>
-      <x:c r="M128" t="inlineStr">
+      <x:c r="M128" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N128" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P128" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z4-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R128" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z4-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W128" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD128" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z4-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z4-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T128" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="W128" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE128" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">树冠步道</x:t>
@@ -15022,6 +15244,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ128" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY128" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ128" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB128" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -15054,10 +15285,8 @@
           <x:t xml:space="preserve">清点采藤记号牌</x:t>
         </x:is>
       </x:c>
-      <x:c r="G129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">数一数步道上还剩几块采藤记号牌。</x:t>
-        </x:is>
+      <x:c r="G129" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I129" t="inlineStr">
         <x:is>
@@ -15074,40 +15303,39 @@
           <x:t xml:space="preserve">ow-npc-mist-4</x:t>
         </x:is>
       </x:c>
-      <x:c r="M129" t="inlineStr">
+      <x:c r="M129" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N129" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P129" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z4-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R129" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z4-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W129" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD129" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z4-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z4-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T129" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U129" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="W129" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE129" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">树冠步道</x:t>
@@ -15134,6 +15362,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ129" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY129" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ129" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB129" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -15218,6 +15455,9 @@
       <x:c r="AQ130" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY130" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="inlineStr">
@@ -15242,7 +15482,7 @@
         <x:v>步道清扫</x:v>
       </x:c>
       <x:c r="G131" t="str">
-        <x:v>清掉树冠步道上的 8 只怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K131" t="inlineStr">
         <x:is>
@@ -15253,7 +15493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U131" t="n">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y131" t="inlineStr">
         <x:is>
@@ -15305,7 +15545,7 @@
         <x:v>步道哨长</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>击败把守树冠步道的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K132" t="inlineStr">
         <x:is>
@@ -15316,7 +15556,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U132" t="n">
-        <x:v>40</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Y132" t="inlineStr">
         <x:is>
@@ -15368,7 +15608,7 @@
         <x:v>截断军需线</x:v>
       </x:c>
       <x:c r="G133" t="str">
-        <x:v>击溃树冠步道沿线的 15 名军需队敌人</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K133" t="inlineStr">
         <x:is>
@@ -15379,7 +15619,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U133" t="n">
-        <x:v>60</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="Y133" t="inlineStr">
         <x:is>
@@ -15437,10 +15677,8 @@
           <x:t xml:space="preserve">带难民回渡口</x:t>
         </x:is>
       </x:c>
-      <x:c r="G134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉溪谷里的营地，把一起逃出来的人带回渡口。</x:t>
-        </x:is>
+      <x:c r="G134" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I134" t="inlineStr">
         <x:is>
@@ -15457,40 +15695,39 @@
           <x:t xml:space="preserve">ow-npc-mist-5</x:t>
         </x:is>
       </x:c>
-      <x:c r="M134" t="inlineStr">
+      <x:c r="M134" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P134" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z5-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R134" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z5-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W134" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD134" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z5-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z5-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T134" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U134" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="W134" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE134" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">溪谷便道</x:t>
@@ -15517,6 +15754,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ134" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY134" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ134" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB134" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -15549,10 +15795,8 @@
           <x:t xml:space="preserve">暮界人的路标</x:t>
         </x:is>
       </x:c>
-      <x:c r="G135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">抄下溪谷路边暮界人刻的路标，带给弥迦念。</x:t>
-        </x:is>
+      <x:c r="G135" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I135" t="inlineStr">
         <x:is>
@@ -15569,40 +15813,39 @@
           <x:t xml:space="preserve">ow-npc-mist-5</x:t>
         </x:is>
       </x:c>
-      <x:c r="M135" t="inlineStr">
+      <x:c r="M135" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P135" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z5-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R135" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z5-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W135" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD135" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z5-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z5-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T135" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U135" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="W135" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE135" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">溪谷便道</x:t>
@@ -15629,6 +15872,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ135" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY135" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ135" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB135" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -15713,6 +15965,9 @@
       <x:c r="AQ136" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY136" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="inlineStr">
@@ -15737,7 +15992,7 @@
         <x:v>溪边游荡者</x:v>
       </x:c>
       <x:c r="G137" t="str">
-        <x:v>赶走溪谷便道上的 8 只怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K137" t="inlineStr">
         <x:is>
@@ -15748,7 +16003,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U137" t="n">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y137" t="inlineStr">
         <x:is>
@@ -15800,7 +16055,7 @@
         <x:v>便道主宰</x:v>
       </x:c>
       <x:c r="G138" t="str">
-        <x:v>击败占住溪谷便道的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K138" t="inlineStr">
         <x:is>
@@ -15811,7 +16066,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U138" t="n">
-        <x:v>40</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Y138" t="inlineStr">
         <x:is>
@@ -15863,7 +16118,7 @@
         <x:v>疏通便道</x:v>
       </x:c>
       <x:c r="G139" t="str">
-        <x:v>肃清溪谷便道两侧的 15 只敌人</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K139" t="inlineStr">
         <x:is>
@@ -15874,7 +16129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U139" t="n">
-        <x:v>60</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="Y139" t="inlineStr">
         <x:is>
@@ -15932,10 +16187,8 @@
           <x:t xml:space="preserve">取回工匠的工具</x:t>
         </x:is>
       </x:c>
-      <x:c r="G140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清掉军需营的营地，抢回斧头被收走的工具。</x:t>
-        </x:is>
+      <x:c r="G140" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I140" t="inlineStr">
         <x:is>
@@ -15952,40 +16205,39 @@
           <x:t xml:space="preserve">ow-npc-mist-6</x:t>
         </x:is>
       </x:c>
-      <x:c r="M140" t="inlineStr">
+      <x:c r="M140" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P140" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z6-1:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R140" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z6-1:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W140" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD140" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z6-1:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z6-1:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T140" t="n">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U140" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W140" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE140" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">军需营</x:t>
@@ -16012,6 +16264,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ140" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY140" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ140" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB140" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -16044,10 +16305,8 @@
           <x:t xml:space="preserve">军需营的派工单</x:t>
         </x:is>
       </x:c>
-      <x:c r="G141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">找出派工单，看军需营逼斧头修了什么。</x:t>
-        </x:is>
+      <x:c r="G141" t="str">
+        <x:v>通关 雾铃 · 雾铃树穴。</x:v>
       </x:c>
       <x:c r="I141" t="inlineStr">
         <x:is>
@@ -16064,40 +16323,39 @@
           <x:t xml:space="preserve">ow-npc-mist-6</x:t>
         </x:is>
       </x:c>
-      <x:c r="M141" t="inlineStr">
+      <x:c r="M141" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>hall</x:v>
+      </x:c>
+      <x:c r="P141" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z6-2:accept</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R141" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ow-mist-side-z6-2:complete</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W141" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD141" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ss-map-mist</x:t>
         </x:is>
       </x:c>
-      <x:c r="N141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-resident6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z6-2:accept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-mist-side-z6-2:complete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T141" t="n">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="U141" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W141" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-mist</x:t>
-        </x:is>
-      </x:c>
       <x:c r="AE141" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">军需营</x:t>
@@ -16124,6 +16382,15 @@
         </x:is>
       </x:c>
       <x:c r="AQ141" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY141" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ141" t="str">
+        <x:v>mist-nest-1</x:v>
+      </x:c>
+      <x:c r="BB141" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -16208,6 +16475,9 @@
       <x:c r="AQ142" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY142" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" t="inlineStr">
@@ -16232,7 +16502,7 @@
         <x:v>营外哨兵</x:v>
       </x:c>
       <x:c r="G143" t="str">
-        <x:v>击退军需营外的 8 名哨兵与怪物</x:v>
+        <x:v>在雾铃任意节点中击败 8 名敌人。</x:v>
       </x:c>
       <x:c r="K143" t="inlineStr">
         <x:is>
@@ -16243,7 +16513,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U143" t="n">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Y143" t="inlineStr">
         <x:is>
@@ -16295,7 +16565,7 @@
         <x:v>营门守将</x:v>
       </x:c>
       <x:c r="G144" t="str">
-        <x:v>击败守在军需营门前的 1 只精英</x:v>
+        <x:v>在雾铃任意节点中击败 1 名精英。</x:v>
       </x:c>
       <x:c r="K144" t="inlineStr">
         <x:is>
@@ -16306,7 +16576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U144" t="n">
-        <x:v>40</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Y144" t="inlineStr">
         <x:is>
@@ -16358,7 +16628,7 @@
         <x:v>瓦解外营</x:v>
       </x:c>
       <x:c r="G145" t="str">
-        <x:v>消灭军需营外营的 15 名敌人，削弱守备</x:v>
+        <x:v>在雾铃任意节点中击败 15 名敌人。</x:v>
       </x:c>
       <x:c r="K145" t="inlineStr">
         <x:is>
@@ -16369,7 +16639,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U145" t="n">
-        <x:v>60</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="Y145" t="inlineStr">
         <x:is>
@@ -16494,6 +16764,9 @@
       <x:c r="AQ146" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY146" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" t="inlineStr">
@@ -16591,6 +16864,9 @@
       <x:c r="AQ147" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY147" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" t="inlineStr">
@@ -16688,6 +16964,9 @@
       <x:c r="AQ148" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AY148" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" t="inlineStr">
@@ -17254,7 +17533,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U154" t="n">
-        <x:v>20</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Y154" t="inlineStr">
         <x:is>
@@ -17317,7 +17596,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U155" t="n">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y155" t="inlineStr">
         <x:is>
@@ -17380,7 +17659,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U156" t="n">
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="Y156" t="inlineStr">
         <x:is>
@@ -17749,7 +18028,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U160" t="n">
-        <x:v>20</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Y160" t="inlineStr">
         <x:is>
@@ -17812,7 +18091,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U161" t="n">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y161" t="inlineStr">
         <x:is>
@@ -17875,7 +18154,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U162" t="n">
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="Y162" t="inlineStr">
         <x:is>
@@ -18244,7 +18523,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U166" t="n">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Y166" t="inlineStr">
         <x:is>
@@ -18307,7 +18586,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U167" t="n">
-        <x:v>40</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="Y167" t="inlineStr">
         <x:is>
@@ -18370,7 +18649,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U168" t="n">
-        <x:v>60</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Y168" t="inlineStr">
         <x:is>
@@ -18739,7 +19018,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U172" t="n">
-        <x:v>20</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y172" t="inlineStr">
         <x:is>
@@ -18802,7 +19081,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U173" t="n">
-        <x:v>40</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="Y173" t="inlineStr">
         <x:is>
@@ -18865,7 +19144,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U174" t="n">
-        <x:v>60</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="Y174" t="inlineStr">
         <x:is>
@@ -19234,7 +19513,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U178" t="n">
-        <x:v>20</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Y178" t="inlineStr">
         <x:is>
@@ -19297,7 +19576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U179" t="n">
-        <x:v>40</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="Y179" t="inlineStr">
         <x:is>
@@ -19360,7 +19639,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U180" t="n">
-        <x:v>60</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="Y180" t="inlineStr">
         <x:is>
@@ -19729,7 +20008,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U184" t="n">
-        <x:v>20</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="Y184" t="inlineStr">
         <x:is>
@@ -19792,7 +20071,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U185" t="n">
-        <x:v>40</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="Y185" t="inlineStr">
         <x:is>
@@ -19855,7 +20134,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U186" t="n">
-        <x:v>60</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="Y186" t="inlineStr">
         <x:is>
@@ -20740,7 +21019,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U195" t="n">
-        <x:v>20</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="Y195" t="inlineStr">
         <x:is>
@@ -20803,7 +21082,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U196" t="n">
-        <x:v>40</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Y196" t="inlineStr">
         <x:is>
@@ -20866,7 +21145,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U197" t="n">
-        <x:v>60</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="Y197" t="inlineStr">
         <x:is>
@@ -21235,7 +21514,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U201" t="n">
-        <x:v>20</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="Y201" t="inlineStr">
         <x:is>
@@ -21298,7 +21577,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U202" t="n">
-        <x:v>40</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Y202" t="inlineStr">
         <x:is>
@@ -21361,7 +21640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U203" t="n">
-        <x:v>60</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="Y203" t="inlineStr">
         <x:is>
@@ -21730,7 +22009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U207" t="n">
-        <x:v>20</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="Y207" t="inlineStr">
         <x:is>
@@ -21793,7 +22072,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U208" t="n">
-        <x:v>40</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="Y208" t="inlineStr">
         <x:is>
@@ -21856,7 +22135,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U209" t="n">
-        <x:v>60</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="Y209" t="inlineStr">
         <x:is>
@@ -22225,7 +22504,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U213" t="n">
-        <x:v>20</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Y213" t="inlineStr">
         <x:is>
@@ -22288,7 +22567,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U214" t="n">
-        <x:v>40</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Y214" t="inlineStr">
         <x:is>
@@ -22351,7 +22630,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U215" t="n">
-        <x:v>60</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="Y215" t="inlineStr">
         <x:is>
@@ -22720,7 +22999,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U219" t="n">
-        <x:v>20</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="Y219" t="inlineStr">
         <x:is>
@@ -22783,7 +23062,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U220" t="n">
-        <x:v>40</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="Y220" t="inlineStr">
         <x:is>
@@ -22846,7 +23125,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U221" t="n">
-        <x:v>60</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="Y221" t="inlineStr">
         <x:is>
@@ -23215,7 +23494,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U225" t="n">
-        <x:v>20</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="Y225" t="inlineStr">
         <x:is>
@@ -23278,7 +23557,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U226" t="n">
-        <x:v>40</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="Y226" t="inlineStr">
         <x:is>
@@ -23341,7 +23620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U227" t="n">
-        <x:v>60</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="Y227" t="inlineStr">
         <x:is>
@@ -24226,7 +24505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U236" t="n">
-        <x:v>20</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="Y236" t="inlineStr">
         <x:is>
@@ -24289,7 +24568,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U237" t="n">
-        <x:v>40</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="Y237" t="inlineStr">
         <x:is>
@@ -24352,7 +24631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U238" t="n">
-        <x:v>60</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="Y238" t="inlineStr">
         <x:is>
@@ -24721,7 +25000,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U242" t="n">
-        <x:v>20</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="Y242" t="inlineStr">
         <x:is>
@@ -24784,7 +25063,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U243" t="n">
-        <x:v>40</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="Y243" t="inlineStr">
         <x:is>
@@ -24847,7 +25126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U244" t="n">
-        <x:v>60</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="Y244" t="inlineStr">
         <x:is>
@@ -25216,7 +25495,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U248" t="n">
-        <x:v>20</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="Y248" t="inlineStr">
         <x:is>
@@ -25279,7 +25558,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U249" t="n">
-        <x:v>40</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="Y249" t="inlineStr">
         <x:is>
@@ -25342,7 +25621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U250" t="n">
-        <x:v>60</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="Y250" t="inlineStr">
         <x:is>
@@ -25711,7 +25990,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U254" t="n">
-        <x:v>20</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="Y254" t="inlineStr">
         <x:is>
@@ -25774,7 +26053,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U255" t="n">
-        <x:v>40</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="Y255" t="inlineStr">
         <x:is>
@@ -25837,7 +26116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U256" t="n">
-        <x:v>60</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="Y256" t="inlineStr">
         <x:is>
@@ -26206,7 +26485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U260" t="n">
-        <x:v>20</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="Y260" t="inlineStr">
         <x:is>
@@ -26269,7 +26548,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U261" t="n">
-        <x:v>40</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="Y261" t="inlineStr">
         <x:is>
@@ -26332,7 +26611,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U262" t="n">
-        <x:v>60</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="Y262" t="inlineStr">
         <x:is>
@@ -26701,7 +26980,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U266" t="n">
-        <x:v>20</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="Y266" t="inlineStr">
         <x:is>
@@ -26764,7 +27043,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U267" t="n">
-        <x:v>40</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="Y267" t="inlineStr">
         <x:is>
@@ -26827,7 +27106,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U268" t="n">
-        <x:v>60</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="Y268" t="inlineStr">
         <x:is>
@@ -27712,7 +27991,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U277" t="n">
-        <x:v>20</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="Y277" t="inlineStr">
         <x:is>
@@ -27775,7 +28054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U278" t="n">
-        <x:v>40</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="Y278" t="inlineStr">
         <x:is>
@@ -27838,7 +28117,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U279" t="n">
-        <x:v>60</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="Y279" t="inlineStr">
         <x:is>
@@ -28207,7 +28486,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U283" t="n">
-        <x:v>20</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="Y283" t="inlineStr">
         <x:is>
@@ -28270,7 +28549,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U284" t="n">
-        <x:v>40</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="Y284" t="inlineStr">
         <x:is>
@@ -28333,7 +28612,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U285" t="n">
-        <x:v>60</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="Y285" t="inlineStr">
         <x:is>
@@ -28702,7 +28981,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U289" t="n">
-        <x:v>20</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="Y289" t="inlineStr">
         <x:is>
@@ -28765,7 +29044,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U290" t="n">
-        <x:v>40</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Y290" t="inlineStr">
         <x:is>
@@ -28828,7 +29107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U291" t="n">
-        <x:v>60</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="Y291" t="inlineStr">
         <x:is>
@@ -29197,7 +29476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U295" t="n">
-        <x:v>20</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="Y295" t="inlineStr">
         <x:is>
@@ -29260,7 +29539,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U296" t="n">
-        <x:v>40</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Y296" t="inlineStr">
         <x:is>
@@ -29323,7 +29602,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U297" t="n">
-        <x:v>60</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="Y297" t="inlineStr">
         <x:is>
@@ -29692,7 +29971,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U301" t="n">
-        <x:v>20</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="Y301" t="inlineStr">
         <x:is>
@@ -29755,7 +30034,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U302" t="n">
-        <x:v>40</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="Y302" t="inlineStr">
         <x:is>
@@ -29818,7 +30097,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U303" t="n">
-        <x:v>60</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="Y303" t="inlineStr">
         <x:is>
@@ -30187,7 +30466,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U307" t="n">
-        <x:v>20</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="Y307" t="inlineStr">
         <x:is>
@@ -30250,7 +30529,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U308" t="n">
-        <x:v>40</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="Y308" t="inlineStr">
         <x:is>
@@ -30313,7 +30592,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U309" t="n">
-        <x:v>60</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="Y309" t="inlineStr">
         <x:is>
@@ -30653,7 +30932,7 @@
         <x:v>旧信上的六角印</x:v>
       </x:c>
       <x:c r="G313" s="17" t="str">
-        <x:v>清退 z2 侵军 → 拾取任一海克斯符文 → 回青芒交付。</x:v>
+        <x:v>清退 z2 侵军，拾取一件带六角印的装备，回青芒交付</x:v>
       </x:c>
       <x:c r="H313" s="17"/>
       <x:c r="I313" s="17" t="str">
@@ -30667,10 +30946,10 @@
         <x:v>ss-npc-qingmang</x:v>
       </x:c>
       <x:c r="M313" s="17" t="str">
-        <x:v>ss-map-mist</x:v>
+        <x:v>ss-map-port</x:v>
       </x:c>
       <x:c r="N313" s="17" t="str">
-        <x:v>ow-mist-resident2</x:v>
+        <x:v>landing</x:v>
       </x:c>
       <x:c r="O313" s="17"/>
       <x:c r="P313" s="17" t="str">
@@ -30682,10 +30961,10 @@
       </x:c>
       <x:c r="S313" s="17"/>
       <x:c r="T313" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>2232</x:v>
       </x:c>
       <x:c r="U313" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="V313" s="17"/>
       <x:c r="W313" s="18" t="b">
@@ -30711,9 +30990,7 @@
       <x:c r="AM313" s="17"/>
       <x:c r="AN313" s="17"/>
       <x:c r="AO313" s="17"/>
-      <x:c r="AP313" s="17" t="str">
-        <x:v>ow-mist-z2</x:v>
-      </x:c>
+      <x:c r="AP313" s="17"/>
       <x:c r="AQ313" s="18" t="b">
         <x:v>0</x:v>
       </x:c>
@@ -30721,12 +30998,8 @@
       <x:c r="AS313" s="17"/>
       <x:c r="AT313" s="17"/>
       <x:c r="AU313" s="17"/>
-      <x:c r="AV313" s="17" t="str">
-        <x:v>hex1</x:v>
-      </x:c>
-      <x:c r="AW313" s="17" t="str">
-        <x:v>{"quality":"common","count":4}</x:v>
-      </x:c>
+      <x:c r="AV313" s="17"/>
+      <x:c r="AW313" s="17"/>
       <x:c r="AX313" s="17"/>
     </x:row>
     <x:row r="314" ht="120" customHeight="1">
@@ -30749,7 +31022,7 @@
         <x:v>印记的主人</x:v>
       </x:c>
       <x:c r="G314" s="17" t="str">
-        <x:v>装备一枚到槽 → 在雾铃击败首领 → 回铜铃。</x:v>
+        <x:v>穿上带六角印的装备，在雾铃击败首领，回铜铃交付</x:v>
       </x:c>
       <x:c r="H314" s="17"/>
       <x:c r="I314" s="17" t="str">
@@ -30780,10 +31053,10 @@
       </x:c>
       <x:c r="S314" s="17"/>
       <x:c r="T314" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>3341</x:v>
       </x:c>
       <x:c r="U314" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="V314" s="17"/>
       <x:c r="W314" s="18" t="b">
@@ -30817,13 +31090,9 @@
       <x:c r="AS314" s="17"/>
       <x:c r="AT314" s="17"/>
       <x:c r="AU314" s="17"/>
-      <x:c r="AV314" s="17" t="str">
-        <x:v>hex2</x:v>
-      </x:c>
+      <x:c r="AV314" s="17"/>
       <x:c r="AW314" s="17"/>
-      <x:c r="AX314" s="17" t="n">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="AX314" s="17"/>
     </x:row>
     <x:row r="315" ht="120" customHeight="1">
       <x:c r="A315" s="17" t="str">
@@ -30868,10 +31137,10 @@
       </x:c>
       <x:c r="S315" s="17"/>
       <x:c r="T315" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>6121</x:v>
       </x:c>
       <x:c r="U315" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="V315" s="17"/>
       <x:c r="W315" s="18" t="b">
@@ -30906,14 +31175,544 @@
       <x:c r="AT315" s="17"/>
       <x:c r="AU315" s="17"/>
       <x:c r="AV315" s="17"/>
-      <x:c r="AW315" s="17" t="str">
-        <x:v>{"quality":"magic","count":3}</x:v>
-      </x:c>
+      <x:c r="AW315" s="17"/>
       <x:c r="AX315" s="17"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" t="str">
+        <x:v>hub-first-return</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>ss-c01</x:v>
+      </x:c>
+      <x:c r="D316" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="E316" t="str">
+        <x:v>guide</x:v>
+      </x:c>
+      <x:c r="F316" t="str">
+        <x:v>第一次回港</x:v>
+      </x:c>
+      <x:c r="G316" t="str">
+        <x:v>去工坊找铜铃</x:v>
+      </x:c>
+      <x:c r="H316"/>
+      <x:c r="I316" t="str">
+        <x:v>ss-npc-tongling</x:v>
+      </x:c>
+      <x:c r="J316"/>
+      <x:c r="K316" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L316"/>
+      <x:c r="M316"/>
+      <x:c r="N316"/>
+      <x:c r="O316"/>
+      <x:c r="P316" t="str">
+        <x:v>hub:first-return:1</x:v>
+      </x:c>
+      <x:c r="Q316"/>
+      <x:c r="R316" t="str">
+        <x:v>hub:first-return:2</x:v>
+      </x:c>
+      <x:c r="S316"/>
+      <x:c r="T316" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U316" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V316" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W316" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X316"/>
+      <x:c r="Y316"/>
+      <x:c r="Z316"/>
+      <x:c r="AA316"/>
+      <x:c r="AB316"/>
+      <x:c r="AC316"/>
+      <x:c r="AD316"/>
+      <x:c r="AE316"/>
+      <x:c r="AF316"/>
+      <x:c r="AG316" t="str">
+        <x:v>港口引导</x:v>
+      </x:c>
+      <x:c r="AH316"/>
+      <x:c r="AI316"/>
+      <x:c r="AJ316"/>
+      <x:c r="AK316"/>
+      <x:c r="AL316" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM316"/>
+      <x:c r="AN316"/>
+      <x:c r="AO316"/>
+      <x:c r="AP316"/>
+      <x:c r="AQ316"/>
+      <x:c r="AR316" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS316"/>
+      <x:c r="AT316"/>
+      <x:c r="AU316"/>
+      <x:c r="AV316"/>
+      <x:c r="AW316"/>
+      <x:c r="AX316"/>
+      <x:c r="AY316"/>
+      <x:c r="AZ316"/>
+      <x:c r="BA316"/>
+      <x:c r="BB316"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" t="str">
+        <x:v>hub-gate-wind-nests</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>ss-c01</x:v>
+      </x:c>
+      <x:c r="D317" t="n">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="E317" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F317" t="str">
+        <x:v>风栖关口：通关两个巢穴</x:v>
+      </x:c>
+      <x:c r="G317" t="str">
+        <x:v>通关两个巢穴</x:v>
+      </x:c>
+      <x:c r="H317"/>
+      <x:c r="I317" t="str">
+        <x:v>ss-npc-milo</x:v>
+      </x:c>
+      <x:c r="J317"/>
+      <x:c r="K317" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L317"/>
+      <x:c r="M317"/>
+      <x:c r="N317"/>
+      <x:c r="O317"/>
+      <x:c r="P317"/>
+      <x:c r="Q317"/>
+      <x:c r="R317"/>
+      <x:c r="S317"/>
+      <x:c r="T317" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U317" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V317" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W317" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X317"/>
+      <x:c r="Y317"/>
+      <x:c r="Z317"/>
+      <x:c r="AA317"/>
+      <x:c r="AB317"/>
+      <x:c r="AC317"/>
+      <x:c r="AD317"/>
+      <x:c r="AE317"/>
+      <x:c r="AF317"/>
+      <x:c r="AG317" t="str">
+        <x:v>关口任务</x:v>
+      </x:c>
+      <x:c r="AH317"/>
+      <x:c r="AI317"/>
+      <x:c r="AJ317"/>
+      <x:c r="AK317"/>
+      <x:c r="AL317" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM317"/>
+      <x:c r="AN317"/>
+      <x:c r="AO317"/>
+      <x:c r="AP317"/>
+      <x:c r="AQ317"/>
+      <x:c r="AR317" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS317"/>
+      <x:c r="AT317"/>
+      <x:c r="AU317"/>
+      <x:c r="AV317"/>
+      <x:c r="AW317"/>
+      <x:c r="AX317"/>
+      <x:c r="AY317"/>
+      <x:c r="AZ317"/>
+      <x:c r="BA317"/>
+      <x:c r="BB317"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" t="str">
+        <x:v>hub-gate-wind-enhance</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>ss-c01</x:v>
+      </x:c>
+      <x:c r="D318" t="n">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="E318" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F318" t="str">
+        <x:v>风栖关口：在工坊强化一次</x:v>
+      </x:c>
+      <x:c r="G318" t="str">
+        <x:v>在工坊强化一次</x:v>
+      </x:c>
+      <x:c r="H318"/>
+      <x:c r="I318" t="str">
+        <x:v>ss-npc-tongling</x:v>
+      </x:c>
+      <x:c r="J318"/>
+      <x:c r="K318" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L318"/>
+      <x:c r="M318"/>
+      <x:c r="N318"/>
+      <x:c r="O318"/>
+      <x:c r="P318"/>
+      <x:c r="Q318"/>
+      <x:c r="R318"/>
+      <x:c r="S318"/>
+      <x:c r="T318" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U318" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V318" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W318" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X318"/>
+      <x:c r="Y318"/>
+      <x:c r="Z318"/>
+      <x:c r="AA318"/>
+      <x:c r="AB318"/>
+      <x:c r="AC318"/>
+      <x:c r="AD318"/>
+      <x:c r="AE318"/>
+      <x:c r="AF318"/>
+      <x:c r="AG318" t="str">
+        <x:v>关口任务</x:v>
+      </x:c>
+      <x:c r="AH318"/>
+      <x:c r="AI318"/>
+      <x:c r="AJ318"/>
+      <x:c r="AK318"/>
+      <x:c r="AL318" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM318"/>
+      <x:c r="AN318"/>
+      <x:c r="AO318"/>
+      <x:c r="AP318"/>
+      <x:c r="AQ318"/>
+      <x:c r="AR318" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS318"/>
+      <x:c r="AT318"/>
+      <x:c r="AU318"/>
+      <x:c r="AV318"/>
+      <x:c r="AW318"/>
+      <x:c r="AX318"/>
+      <x:c r="AY318"/>
+      <x:c r="AZ318"/>
+      <x:c r="BA318"/>
+      <x:c r="BB318"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" t="str">
+        <x:v>hub-gate-mist-hex</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>ss-c02</x:v>
+      </x:c>
+      <x:c r="D319" t="n">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="E319" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F319" t="str">
+        <x:v>雾铃关口：穿戴海克斯</x:v>
+      </x:c>
+      <x:c r="G319" t="str">
+        <x:v>穿上一件带「◆」的装备</x:v>
+      </x:c>
+      <x:c r="H319"/>
+      <x:c r="I319" t="str">
+        <x:v>ss-npc-qingmang</x:v>
+      </x:c>
+      <x:c r="J319"/>
+      <x:c r="K319" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L319"/>
+      <x:c r="M319"/>
+      <x:c r="N319"/>
+      <x:c r="O319"/>
+      <x:c r="P319"/>
+      <x:c r="Q319"/>
+      <x:c r="R319"/>
+      <x:c r="S319"/>
+      <x:c r="T319" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U319" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V319" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W319" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X319"/>
+      <x:c r="Y319"/>
+      <x:c r="Z319"/>
+      <x:c r="AA319"/>
+      <x:c r="AB319"/>
+      <x:c r="AC319"/>
+      <x:c r="AD319"/>
+      <x:c r="AE319"/>
+      <x:c r="AF319"/>
+      <x:c r="AG319" t="str">
+        <x:v>关口任务</x:v>
+      </x:c>
+      <x:c r="AH319"/>
+      <x:c r="AI319"/>
+      <x:c r="AJ319"/>
+      <x:c r="AK319"/>
+      <x:c r="AL319" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM319"/>
+      <x:c r="AN319"/>
+      <x:c r="AO319"/>
+      <x:c r="AP319"/>
+      <x:c r="AQ319"/>
+      <x:c r="AR319" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS319"/>
+      <x:c r="AT319"/>
+      <x:c r="AU319"/>
+      <x:c r="AV319"/>
+      <x:c r="AW319"/>
+      <x:c r="AX319"/>
+      <x:c r="AY319"/>
+      <x:c r="AZ319"/>
+      <x:c r="BA319"/>
+      <x:c r="BB319"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" t="str">
+        <x:v>hub-gate-mist-talent</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>ss-c02</x:v>
+      </x:c>
+      <x:c r="D320" t="n">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="E320" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F320" t="str">
+        <x:v>雾铃关口：分配天赋</x:v>
+      </x:c>
+      <x:c r="G320" t="str">
+        <x:v>点一个天赋</x:v>
+      </x:c>
+      <x:c r="H320"/>
+      <x:c r="I320" t="str">
+        <x:v>ss-npc-cheng</x:v>
+      </x:c>
+      <x:c r="J320"/>
+      <x:c r="K320" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L320"/>
+      <x:c r="M320"/>
+      <x:c r="N320"/>
+      <x:c r="O320"/>
+      <x:c r="P320"/>
+      <x:c r="Q320"/>
+      <x:c r="R320"/>
+      <x:c r="S320"/>
+      <x:c r="T320" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U320" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V320" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W320" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X320"/>
+      <x:c r="Y320"/>
+      <x:c r="Z320"/>
+      <x:c r="AA320"/>
+      <x:c r="AB320"/>
+      <x:c r="AC320"/>
+      <x:c r="AD320"/>
+      <x:c r="AE320"/>
+      <x:c r="AF320"/>
+      <x:c r="AG320" t="str">
+        <x:v>关口任务</x:v>
+      </x:c>
+      <x:c r="AH320"/>
+      <x:c r="AI320"/>
+      <x:c r="AJ320"/>
+      <x:c r="AK320"/>
+      <x:c r="AL320" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM320"/>
+      <x:c r="AN320"/>
+      <x:c r="AO320"/>
+      <x:c r="AP320"/>
+      <x:c r="AQ320"/>
+      <x:c r="AR320" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS320"/>
+      <x:c r="AT320"/>
+      <x:c r="AU320"/>
+      <x:c r="AV320"/>
+      <x:c r="AW320"/>
+      <x:c r="AX320"/>
+      <x:c r="AY320"/>
+      <x:c r="AZ320"/>
+      <x:c r="BA320"/>
+      <x:c r="BB320"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" t="str">
+        <x:v>hub-gate-mist-dispatch</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>ss-c02</x:v>
+      </x:c>
+      <x:c r="D321" t="n">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="E321" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F321" t="str">
+        <x:v>雾铃关口：派遣船队</x:v>
+      </x:c>
+      <x:c r="G321" t="str">
+        <x:v>派一次采集船队</x:v>
+      </x:c>
+      <x:c r="H321"/>
+      <x:c r="I321" t="str">
+        <x:v>ss-npc-milo</x:v>
+      </x:c>
+      <x:c r="J321"/>
+      <x:c r="K321" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L321"/>
+      <x:c r="M321"/>
+      <x:c r="N321"/>
+      <x:c r="O321"/>
+      <x:c r="P321"/>
+      <x:c r="Q321"/>
+      <x:c r="R321"/>
+      <x:c r="S321"/>
+      <x:c r="T321" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U321" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V321" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W321" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X321"/>
+      <x:c r="Y321"/>
+      <x:c r="Z321"/>
+      <x:c r="AA321"/>
+      <x:c r="AB321"/>
+      <x:c r="AC321"/>
+      <x:c r="AD321"/>
+      <x:c r="AE321"/>
+      <x:c r="AF321"/>
+      <x:c r="AG321" t="str">
+        <x:v>关口任务</x:v>
+      </x:c>
+      <x:c r="AH321"/>
+      <x:c r="AI321"/>
+      <x:c r="AJ321"/>
+      <x:c r="AK321"/>
+      <x:c r="AL321" t="str">
+        <x:v>hub-guide</x:v>
+      </x:c>
+      <x:c r="AM321"/>
+      <x:c r="AN321"/>
+      <x:c r="AO321"/>
+      <x:c r="AP321"/>
+      <x:c r="AQ321"/>
+      <x:c r="AR321" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS321"/>
+      <x:c r="AT321"/>
+      <x:c r="AU321"/>
+      <x:c r="AV321"/>
+      <x:c r="AW321"/>
+      <x:c r="AX321"/>
+      <x:c r="AY321"/>
+      <x:c r="AZ321"/>
+      <x:c r="BA321"/>
+      <x:c r="BB321"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbd167ef096f4320"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec7fcc6907244f8"/>
 </x:worksheet>
 </file>
 
@@ -36546,39 +37345,26 @@
       <x:c r="B103" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reach_waypoint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-wp2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">触碰船台湾航标</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">outpost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y103" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-z2</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>hub-guide:near</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>去港口中央的星门</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="L103"/>
+      <x:c r="Y103" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="inlineStr">
@@ -36589,44 +37375,26 @@
       <x:c r="B104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">talk</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">npc:ss-npc-milo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">听米洛介绍前哨</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-map-wind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">outpost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ss-npc-milo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y104" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ow-wind-z2</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>hub-guide:open</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>打开航图</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="L104"/>
+      <x:c r="Y104" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="inlineStr">
@@ -49142,36 +49910,20 @@
       </x:c>
     </x:row>
     <x:row r="379" ht="60" customHeight="1">
-      <x:c r="A379" s="17" t="str">
-        <x:v>HEX-Q01</x:v>
-      </x:c>
-      <x:c r="B379" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C379" s="17" t="str">
-        <x:v>kill_zone</x:v>
-      </x:c>
-      <x:c r="D379" s="17" t="str">
-        <x:v>kill:z2_invader</x:v>
-      </x:c>
+      <x:c r="A379" s="17"/>
+      <x:c r="B379" s="17"/>
+      <x:c r="C379" s="17"/>
+      <x:c r="D379" s="17"/>
       <x:c r="E379" s="17"/>
-      <x:c r="F379" s="17" t="str">
-        <x:v>清退 z2 侵军</x:v>
-      </x:c>
+      <x:c r="F379" s="17"/>
       <x:c r="G379" s="17"/>
-      <x:c r="H379" s="17" t="str">
-        <x:v>ss-map-mist</x:v>
-      </x:c>
-      <x:c r="I379" s="17" t="str">
-        <x:v>ow-mist-camp-clue2</x:v>
-      </x:c>
+      <x:c r="H379" s="17"/>
+      <x:c r="I379" s="17"/>
       <x:c r="J379" s="17"/>
       <x:c r="K379" s="17"/>
       <x:c r="L379" s="17"/>
       <x:c r="M379" s="17"/>
-      <x:c r="N379" s="17" t="n">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="N379" s="17"/>
       <x:c r="O379" s="17"/>
       <x:c r="P379" s="17"/>
       <x:c r="Q379" s="17"/>
@@ -49182,12 +49934,8 @@
       <x:c r="V379" s="17"/>
       <x:c r="W379" s="17"/>
       <x:c r="X379" s="17"/>
-      <x:c r="Y379" s="18" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z379" s="17" t="str">
-        <x:v>ow-mist-z2</x:v>
-      </x:c>
+      <x:c r="Y379" s="17"/>
+      <x:c r="Z379" s="17"/>
       <x:c r="AA379" s="17"/>
       <x:c r="AB379" s="17"/>
       <x:c r="AC379" s="17"/>
@@ -49198,24 +49946,24 @@
         <x:v>HEX-Q01</x:v>
       </x:c>
       <x:c r="B380" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C380" s="17" t="str">
         <x:v>obtain_hex</x:v>
       </x:c>
       <x:c r="D380" s="17" t="str">
-        <x:v>obtain:hex_rune</x:v>
+        <x:v>obtain:hex_gear</x:v>
       </x:c>
       <x:c r="E380" s="17"/>
       <x:c r="F380" s="17" t="str">
-        <x:v>拾取任一海克斯符文</x:v>
+        <x:v>在雾铃任一节点拾取一件带「◆」的装备</x:v>
       </x:c>
       <x:c r="G380" s="17"/>
       <x:c r="H380" s="17" t="str">
         <x:v>ss-map-mist</x:v>
       </x:c>
       <x:c r="I380" s="17" t="str">
-        <x:v>ow-mist-resident2</x:v>
+        <x:v>landing</x:v>
       </x:c>
       <x:c r="J380" s="17"/>
       <x:c r="K380" s="17"/>
@@ -49237,9 +49985,7 @@
       <x:c r="Y380" s="18" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z380" s="17" t="str">
-        <x:v>ow-mist-z2</x:v>
-      </x:c>
+      <x:c r="Z380" s="17"/>
       <x:c r="AA380" s="17"/>
       <x:c r="AB380" s="17"/>
       <x:c r="AC380" s="17"/>
@@ -49250,7 +49996,7 @@
         <x:v>HEX-Q01</x:v>
       </x:c>
       <x:c r="B381" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C381" s="17" t="str">
         <x:v>talk</x:v>
@@ -49260,14 +50006,14 @@
       </x:c>
       <x:c r="E381" s="17"/>
       <x:c r="F381" s="17" t="str">
-        <x:v>回青芒交付</x:v>
+        <x:v>回港交给青芒</x:v>
       </x:c>
       <x:c r="G381" s="17"/>
       <x:c r="H381" s="17" t="str">
-        <x:v>ss-map-mist</x:v>
+        <x:v>ss-map-port</x:v>
       </x:c>
       <x:c r="I381" s="17" t="str">
-        <x:v>ow-mist-resident2</x:v>
+        <x:v>landing</x:v>
       </x:c>
       <x:c r="J381" s="17"/>
       <x:c r="K381" s="17"/>
@@ -49304,11 +50050,11 @@
         <x:v>equip_hex</x:v>
       </x:c>
       <x:c r="D382" s="17" t="str">
-        <x:v>equip:hex_rune</x:v>
+        <x:v>equip:hex_gear</x:v>
       </x:c>
       <x:c r="E382" s="17"/>
       <x:c r="F382" s="17" t="str">
-        <x:v>装备一枚到槽</x:v>
+        <x:v>穿上一件带六角印的装备</x:v>
       </x:c>
       <x:c r="G382" s="17"/>
       <x:c r="H382" s="17" t="str">
@@ -49351,20 +50097,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C383" s="17" t="str">
-        <x:v>boss</x:v>
+        <x:v>hub_fact</x:v>
       </x:c>
       <x:c r="D383" s="17" t="str">
-        <x:v>kill:mist_boss</x:v>
+        <x:v>hub-node:mist-gate</x:v>
       </x:c>
       <x:c r="E383" s="17"/>
       <x:c r="F383" s="17" t="str">
-        <x:v>在雾铃击败首领</x:v>
+        <x:v>通关雾铃关口首领</x:v>
       </x:c>
       <x:c r="G383" s="17"/>
       <x:c r="H383" s="17" t="str">
-        <x:v>ss-map-boss-2</x:v>
-      </x:c>
-      <x:c r="I383" s="17"/>
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I383" s="17" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
       <x:c r="J383" s="17"/>
       <x:c r="K383" s="17"/>
       <x:c r="L383" s="17"/>
@@ -49445,20 +50193,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C385" s="17" t="str">
-        <x:v>boss</x:v>
+        <x:v>hub_fact</x:v>
       </x:c>
       <x:c r="D385" s="17" t="str">
-        <x:v>kill:mist_boss</x:v>
+        <x:v>hub-node:mist-gate</x:v>
       </x:c>
       <x:c r="E385" s="17"/>
       <x:c r="F385" s="17" t="str">
-        <x:v>军需平台首杀后一次性交付</x:v>
+        <x:v>雾铃关口首领首通后一次性交付</x:v>
       </x:c>
       <x:c r="G385" s="17"/>
       <x:c r="H385" s="17" t="str">
-        <x:v>ss-map-boss-2</x:v>
-      </x:c>
-      <x:c r="I385" s="17"/>
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I385" s="17" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
       <x:c r="J385" s="17"/>
       <x:c r="K385" s="17"/>
       <x:c r="L385" s="17"/>
@@ -49485,9 +50235,397 @@
       <x:c r="AC385" s="17"/>
       <x:c r="AD385" s="17"/>
     </x:row>
+    <x:row r="386">
+      <x:c r="A386" t="str">
+        <x:v>ss-c01-n01</x:v>
+      </x:c>
+      <x:c r="B386" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>hub-guide:depart</x:v>
+      </x:c>
+      <x:c r="E386"/>
+      <x:c r="F386" t="str">
+        <x:v>出发：风栖 · 落点求生</x:v>
+      </x:c>
+      <x:c r="G386"/>
+      <x:c r="H386" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I386" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J386"/>
+      <x:c r="K386"/>
+      <x:c r="L386"/>
+      <x:c r="M386"/>
+      <x:c r="N386"/>
+      <x:c r="O386"/>
+      <x:c r="P386"/>
+      <x:c r="Q386"/>
+      <x:c r="R386"/>
+      <x:c r="S386"/>
+      <x:c r="T386"/>
+      <x:c r="U386"/>
+      <x:c r="V386"/>
+      <x:c r="W386"/>
+      <x:c r="X386"/>
+      <x:c r="Y386" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z386"/>
+      <x:c r="AA386"/>
+      <x:c r="AB386"/>
+      <x:c r="AC386"/>
+      <x:c r="AD386"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" t="str">
+        <x:v>hub-first-return</x:v>
+      </x:c>
+      <x:c r="B387" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>talk</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>npc:ss-npc-tongling</x:v>
+      </x:c>
+      <x:c r="E387"/>
+      <x:c r="F387" t="str">
+        <x:v>去工坊找铜铃</x:v>
+      </x:c>
+      <x:c r="G387"/>
+      <x:c r="H387" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I387" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="J387"/>
+      <x:c r="K387"/>
+      <x:c r="L387" t="str">
+        <x:v>ss-npc-tongling</x:v>
+      </x:c>
+      <x:c r="M387"/>
+      <x:c r="N387"/>
+      <x:c r="O387"/>
+      <x:c r="P387"/>
+      <x:c r="Q387"/>
+      <x:c r="R387"/>
+      <x:c r="S387"/>
+      <x:c r="T387"/>
+      <x:c r="U387"/>
+      <x:c r="V387"/>
+      <x:c r="W387"/>
+      <x:c r="X387"/>
+      <x:c r="Y387" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z387"/>
+      <x:c r="AA387"/>
+      <x:c r="AB387"/>
+      <x:c r="AC387"/>
+      <x:c r="AD387"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" t="str">
+        <x:v>hub-first-return</x:v>
+      </x:c>
+      <x:c r="B388" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>talk</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>npc:ss-npc-milo</x:v>
+      </x:c>
+      <x:c r="E388"/>
+      <x:c r="F388" t="str">
+        <x:v>回到星门，挑下一个节点</x:v>
+      </x:c>
+      <x:c r="G388"/>
+      <x:c r="H388" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I388" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J388"/>
+      <x:c r="K388"/>
+      <x:c r="L388" t="str">
+        <x:v>ss-npc-milo</x:v>
+      </x:c>
+      <x:c r="M388"/>
+      <x:c r="N388"/>
+      <x:c r="O388"/>
+      <x:c r="P388"/>
+      <x:c r="Q388"/>
+      <x:c r="R388"/>
+      <x:c r="S388"/>
+      <x:c r="T388"/>
+      <x:c r="U388"/>
+      <x:c r="V388"/>
+      <x:c r="W388"/>
+      <x:c r="X388"/>
+      <x:c r="Y388" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z388"/>
+      <x:c r="AA388"/>
+      <x:c r="AB388"/>
+      <x:c r="AC388"/>
+      <x:c r="AD388"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="str">
+        <x:v>hub-gate-wind-nests</x:v>
+      </x:c>
+      <x:c r="B389" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>hub-gate:wind-nests</x:v>
+      </x:c>
+      <x:c r="E389"/>
+      <x:c r="F389" t="str">
+        <x:v>通关两个巢穴</x:v>
+      </x:c>
+      <x:c r="G389"/>
+      <x:c r="H389" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I389" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J389"/>
+      <x:c r="K389"/>
+      <x:c r="L389"/>
+      <x:c r="M389"/>
+      <x:c r="N389"/>
+      <x:c r="O389"/>
+      <x:c r="P389"/>
+      <x:c r="Q389"/>
+      <x:c r="R389"/>
+      <x:c r="S389"/>
+      <x:c r="T389"/>
+      <x:c r="U389"/>
+      <x:c r="V389"/>
+      <x:c r="W389"/>
+      <x:c r="X389"/>
+      <x:c r="Y389" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z389"/>
+      <x:c r="AA389"/>
+      <x:c r="AB389"/>
+      <x:c r="AC389"/>
+      <x:c r="AD389"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="str">
+        <x:v>hub-gate-wind-enhance</x:v>
+      </x:c>
+      <x:c r="B390" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>hub-gate:enhance</x:v>
+      </x:c>
+      <x:c r="E390"/>
+      <x:c r="F390" t="str">
+        <x:v>在工坊强化一次</x:v>
+      </x:c>
+      <x:c r="G390"/>
+      <x:c r="H390" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I390" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J390"/>
+      <x:c r="K390"/>
+      <x:c r="L390"/>
+      <x:c r="M390"/>
+      <x:c r="N390"/>
+      <x:c r="O390"/>
+      <x:c r="P390"/>
+      <x:c r="Q390"/>
+      <x:c r="R390"/>
+      <x:c r="S390"/>
+      <x:c r="T390"/>
+      <x:c r="U390"/>
+      <x:c r="V390"/>
+      <x:c r="W390"/>
+      <x:c r="X390"/>
+      <x:c r="Y390" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z390"/>
+      <x:c r="AA390"/>
+      <x:c r="AB390"/>
+      <x:c r="AC390"/>
+      <x:c r="AD390"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="str">
+        <x:v>hub-gate-mist-hex</x:v>
+      </x:c>
+      <x:c r="B391" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>hub-gate:equip-hex</x:v>
+      </x:c>
+      <x:c r="E391"/>
+      <x:c r="F391" t="str">
+        <x:v>穿上一件带「◆」的装备</x:v>
+      </x:c>
+      <x:c r="G391"/>
+      <x:c r="H391" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I391" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J391"/>
+      <x:c r="K391"/>
+      <x:c r="L391"/>
+      <x:c r="M391"/>
+      <x:c r="N391"/>
+      <x:c r="O391"/>
+      <x:c r="P391"/>
+      <x:c r="Q391"/>
+      <x:c r="R391"/>
+      <x:c r="S391"/>
+      <x:c r="T391"/>
+      <x:c r="U391"/>
+      <x:c r="V391"/>
+      <x:c r="W391"/>
+      <x:c r="X391"/>
+      <x:c r="Y391" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z391"/>
+      <x:c r="AA391"/>
+      <x:c r="AB391"/>
+      <x:c r="AC391"/>
+      <x:c r="AD391"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="str">
+        <x:v>hub-gate-mist-talent</x:v>
+      </x:c>
+      <x:c r="B392" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>hub-gate:talent</x:v>
+      </x:c>
+      <x:c r="E392"/>
+      <x:c r="F392" t="str">
+        <x:v>点一个天赋</x:v>
+      </x:c>
+      <x:c r="G392"/>
+      <x:c r="H392" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I392" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J392"/>
+      <x:c r="K392"/>
+      <x:c r="L392"/>
+      <x:c r="M392"/>
+      <x:c r="N392"/>
+      <x:c r="O392"/>
+      <x:c r="P392"/>
+      <x:c r="Q392"/>
+      <x:c r="R392"/>
+      <x:c r="S392"/>
+      <x:c r="T392"/>
+      <x:c r="U392"/>
+      <x:c r="V392"/>
+      <x:c r="W392"/>
+      <x:c r="X392"/>
+      <x:c r="Y392" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z392"/>
+      <x:c r="AA392"/>
+      <x:c r="AB392"/>
+      <x:c r="AC392"/>
+      <x:c r="AD392"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" t="str">
+        <x:v>hub-gate-mist-dispatch</x:v>
+      </x:c>
+      <x:c r="B393" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>hub-gate:dispatch</x:v>
+      </x:c>
+      <x:c r="E393"/>
+      <x:c r="F393" t="str">
+        <x:v>派一次采集船队</x:v>
+      </x:c>
+      <x:c r="G393"/>
+      <x:c r="H393" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I393" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J393"/>
+      <x:c r="K393"/>
+      <x:c r="L393"/>
+      <x:c r="M393"/>
+      <x:c r="N393"/>
+      <x:c r="O393"/>
+      <x:c r="P393"/>
+      <x:c r="Q393"/>
+      <x:c r="R393"/>
+      <x:c r="S393"/>
+      <x:c r="T393"/>
+      <x:c r="U393"/>
+      <x:c r="V393"/>
+      <x:c r="W393"/>
+      <x:c r="X393"/>
+      <x:c r="Y393" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z393"/>
+      <x:c r="AA393"/>
+      <x:c r="AB393"/>
+      <x:c r="AC393"/>
+      <x:c r="AD393"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c6f300862a480a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51087d28e87043e9"/>
 </x:worksheet>
 </file>
 
@@ -50553,7 +51691,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd527df841518416f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R745f11af0cc44127"/>
 </x:worksheet>
 </file>
 
@@ -67874,7 +69012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C693" s="17" t="str">
-        <x:v>island</x:v>
+        <x:v>island_visited</x:v>
       </x:c>
       <x:c r="D693" s="17" t="str">
         <x:v>ss-map-mist</x:v>
@@ -68036,9 +69174,111 @@
         <x:v>guide</x:v>
       </x:c>
     </x:row>
+    <x:row r="703">
+      <x:c r="A703" t="str">
+        <x:v>hub-first-return</x:v>
+      </x:c>
+      <x:c r="B703" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C703" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D703" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E703" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704">
+      <x:c r="A704" t="str">
+        <x:v>hub-gate-wind-nests</x:v>
+      </x:c>
+      <x:c r="B704" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C704" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D704" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E704" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705">
+      <x:c r="A705" t="str">
+        <x:v>hub-gate-wind-enhance</x:v>
+      </x:c>
+      <x:c r="B705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C705" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D705" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E705" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706">
+      <x:c r="A706" t="str">
+        <x:v>hub-gate-mist-hex</x:v>
+      </x:c>
+      <x:c r="B706" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C706" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D706" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E706" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707">
+      <x:c r="A707" t="str">
+        <x:v>hub-gate-mist-talent</x:v>
+      </x:c>
+      <x:c r="B707" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C707" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D707" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E707" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708">
+      <x:c r="A708" t="str">
+        <x:v>hub-gate-mist-dispatch</x:v>
+      </x:c>
+      <x:c r="B708" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C708" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="D708" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E708" t="str">
+        <x:v>fallback</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb827971fd003446a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e6ec6deeea24a1f"/>
 </x:worksheet>
 </file>
 
@@ -68834,7 +70074,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d3560144fef468e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ccd1f50e5744c5e"/>
 </x:worksheet>
 </file>
 
@@ -69735,6 +70975,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8049419dcab24d13"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8463ef2ba35746cd"/>
 </x:worksheet>
 </file>
--- a/open-world/config/excel/任务.xlsx
+++ b/open-world/config/excel/任务.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb384e06b98c844cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="2" r:id="Rd6f9310fd5f547da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务类型" sheetId="3" r:id="R648a6ef2f61447fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="4" r:id="Rcfb9dd9f6eaa419b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤" sheetId="5" r:id="Rce88293f0a8246a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线" sheetId="6" r:id="R9bd6ca3db4bb4a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件" sheetId="7" r:id="R202ae1e0a74a403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="传闻" sheetId="8" r:id="R79aaad4a6ae94d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能找回" sheetId="9" r:id="Rbd709e079a2a4a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R964649ce2c614870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="2" r:id="R7038dbc906af4176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务类型" sheetId="3" r:id="R706936ad85ca462b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="4" r:id="R427c11d2138441eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤" sheetId="5" r:id="Ra13f9c8839864296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线" sheetId="6" r:id="R49a2f2f16377427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件" sheetId="7" r:id="R6fe00d1fc6bf408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="传闻" sheetId="8" r:id="R9cc16a9c92a84e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能找回" sheetId="9" r:id="Ra4d1caae2bb74624"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,6 +174,7 @@
     <x:author>tc={8B21994E-F85D-4295-A3A0-3E11128245CD}</x:author>
     <x:author>tc={5F050F4B-784D-45ED-9CCE-541796FF516C}</x:author>
     <x:author/>
+    <x:author>tc={11A5B88D-5B8D-44D6-A2A7-40E93B8D413E}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A1" authorId="0">
@@ -553,6 +554,16 @@
       <x:text>
         <x:r>
           <x:t>D12：任务完成发放的回响碎片数量，仅一次。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="BC2" authorId="12">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    首通结算的T1材料，JSON {materialId:非负整数个数}。关口预算记录绑定hub_node且hub_return=true/journal=false：不接取、不展示任务，由现有节点首通事实一次性结算，不参与本日×2。 唯一源：config/excel 工作簿；经 pnpm config:export 导出，服务端消费。数值来自经审核的 B4 推导计划，不在运行时另设第二份配置。</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -1316,6 +1327,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="HUB 配置字段说明" id="{647D2B22-8B16-4115-BD1B-35B9123D397F}"/>
   <xltc:person displayName="tc={094C4E01-3C4C-4447-82A0-FC4FC1A64DCE}" id="{BEFC62CC-411B-A519-36CC-702EF782B778}"/>
   <xltc:person displayName="tc={BF0E8B7E-C8A2-4328-8E42-B20C885C90EE}" id="{A92C1EAE-7AD0-8E1F-762C-433E02D8E1A0}"/>
   <xltc:person displayName="None" id="{A526D1F0-D2D1-FEBE-9CEF-436996D68996}"/>
@@ -1567,6 +1579,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="BC2" dT="2026-10-22T16:19:42.898" personId="{647D2B22-8B16-4115-BD1B-35B9123D397F}" id="{11A5B88D-5B8D-44D6-A2A7-40E93B8D413E}">
+    <xltc:text>首通结算的T1材料，JSON {materialId:非负整数个数}。关口预算记录绑定hub_node且hub_return=true/journal=false：不接取、不展示任务，由现有节点首通事实一次性结算，不参与本日×2。 唯一源：config/excel 工作簿；经 pnpm config:export 导出，服务端消费。数值来自经审核的 B4 推导计划，不在运行时另设第二份配置。</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1905,7 +1925,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe9f7e8eda31480f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc7e971848454d16"/>
 </x:worksheet>
 </file>
 
@@ -2317,7 +2337,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7437344fc7ab4e1a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35d63bf1b1334097"/>
 </x:worksheet>
 </file>
 
@@ -2375,6 +2395,7 @@
     <x:col min="48" max="48" width="24" hidden="0" customWidth="1"/>
     <x:col min="49" max="49" width="24" hidden="0" customWidth="1"/>
     <x:col min="50" max="50" width="24" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="68" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2628,6 +2649,9 @@
       <x:c r="BB1" t="str">
         <x:v>hub_commission</x:v>
       </x:c>
+      <x:c r="BC1" t="str">
+        <x:v>reward_materials</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="inlineStr">
@@ -2880,6 +2904,9 @@
       <x:c r="BB2" t="str">
         <x:v>hub_commission</x:v>
       </x:c>
+      <x:c r="BC2" t="str">
+        <x:v>reward_materials</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="inlineStr">
@@ -3131,6 +3158,9 @@
       </x:c>
       <x:c r="BB3" t="str">
         <x:v>bool</x:v>
+      </x:c>
+      <x:c r="BC3" t="str">
+        <x:v>json</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -31353,7 +31383,9 @@
       <x:c r="AV317"/>
       <x:c r="AW317"/>
       <x:c r="AX317"/>
-      <x:c r="AY317"/>
+      <x:c r="AY317" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AZ317"/>
       <x:c r="BA317"/>
       <x:c r="BB317"/>
@@ -31441,7 +31473,9 @@
       <x:c r="AV318"/>
       <x:c r="AW318"/>
       <x:c r="AX318"/>
-      <x:c r="AY318"/>
+      <x:c r="AY318" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AZ318"/>
       <x:c r="BA318"/>
       <x:c r="BB318"/>
@@ -31529,7 +31563,9 @@
       <x:c r="AV319"/>
       <x:c r="AW319"/>
       <x:c r="AX319"/>
-      <x:c r="AY319"/>
+      <x:c r="AY319" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AZ319"/>
       <x:c r="BA319"/>
       <x:c r="BB319"/>
@@ -31617,7 +31653,9 @@
       <x:c r="AV320"/>
       <x:c r="AW320"/>
       <x:c r="AX320"/>
-      <x:c r="AY320"/>
+      <x:c r="AY320" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AZ320"/>
       <x:c r="BA320"/>
       <x:c r="BB320"/>
@@ -31705,14 +31743,210 @@
       <x:c r="AV321"/>
       <x:c r="AW321"/>
       <x:c r="AX321"/>
-      <x:c r="AY321"/>
+      <x:c r="AY321" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AZ321"/>
       <x:c r="BA321"/>
       <x:c r="BB321"/>
     </x:row>
+    <x:row r="322">
+      <x:c r="A322" t="str">
+        <x:v>hub-gate-reward-wind</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>ss-c01</x:v>
+      </x:c>
+      <x:c r="D322" t="n">
+        <x:v>9004</x:v>
+      </x:c>
+      <x:c r="E322" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F322" t="str">
+        <x:v>击退登港先锋首通奖励</x:v>
+      </x:c>
+      <x:c r="G322" t="str">
+        <x:v>击退登港先锋首通奖励</x:v>
+      </x:c>
+      <x:c r="H322"/>
+      <x:c r="I322" t="str">
+        <x:v>ss-npc-milo</x:v>
+      </x:c>
+      <x:c r="J322"/>
+      <x:c r="K322" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L322"/>
+      <x:c r="M322"/>
+      <x:c r="N322"/>
+      <x:c r="O322"/>
+      <x:c r="P322"/>
+      <x:c r="Q322"/>
+      <x:c r="R322"/>
+      <x:c r="S322"/>
+      <x:c r="T322" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U322" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V322" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W322" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X322"/>
+      <x:c r="Y322"/>
+      <x:c r="Z322"/>
+      <x:c r="AA322"/>
+      <x:c r="AB322"/>
+      <x:c r="AC322"/>
+      <x:c r="AD322"/>
+      <x:c r="AE322"/>
+      <x:c r="AF322"/>
+      <x:c r="AG322" t="str">
+        <x:v>["首通结算"]</x:v>
+      </x:c>
+      <x:c r="AH322"/>
+      <x:c r="AI322"/>
+      <x:c r="AJ322"/>
+      <x:c r="AK322"/>
+      <x:c r="AL322" t="str">
+        <x:v>hub-first-clear-reward</x:v>
+      </x:c>
+      <x:c r="AM322"/>
+      <x:c r="AN322"/>
+      <x:c r="AO322"/>
+      <x:c r="AP322"/>
+      <x:c r="AQ322"/>
+      <x:c r="AR322" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS322"/>
+      <x:c r="AT322"/>
+      <x:c r="AU322"/>
+      <x:c r="AV322"/>
+      <x:c r="AW322"/>
+      <x:c r="AX322"/>
+      <x:c r="AY322" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ322" t="str">
+        <x:v>wind-gate</x:v>
+      </x:c>
+      <x:c r="BA322" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB322"/>
+      <x:c r="BC322" t="str">
+        <x:v>{"wind_ore":4,"wind_herb":4}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" t="str">
+        <x:v>hub-gate-reward-mist</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>starsea</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>ss-c02</x:v>
+      </x:c>
+      <x:c r="D323" t="n">
+        <x:v>9005</x:v>
+      </x:c>
+      <x:c r="E323" t="str">
+        <x:v>side</x:v>
+      </x:c>
+      <x:c r="F323" t="str">
+        <x:v>截击军需官首通奖励</x:v>
+      </x:c>
+      <x:c r="G323" t="str">
+        <x:v>截击军需官首通奖励</x:v>
+      </x:c>
+      <x:c r="H323"/>
+      <x:c r="I323" t="str">
+        <x:v>ss-npc-qingmang</x:v>
+      </x:c>
+      <x:c r="J323"/>
+      <x:c r="K323" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L323"/>
+      <x:c r="M323"/>
+      <x:c r="N323"/>
+      <x:c r="O323"/>
+      <x:c r="P323"/>
+      <x:c r="Q323"/>
+      <x:c r="R323"/>
+      <x:c r="S323"/>
+      <x:c r="T323" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U323" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V323" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W323" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X323"/>
+      <x:c r="Y323"/>
+      <x:c r="Z323"/>
+      <x:c r="AA323"/>
+      <x:c r="AB323"/>
+      <x:c r="AC323"/>
+      <x:c r="AD323"/>
+      <x:c r="AE323"/>
+      <x:c r="AF323"/>
+      <x:c r="AG323" t="str">
+        <x:v>["首通结算"]</x:v>
+      </x:c>
+      <x:c r="AH323"/>
+      <x:c r="AI323"/>
+      <x:c r="AJ323"/>
+      <x:c r="AK323"/>
+      <x:c r="AL323" t="str">
+        <x:v>hub-first-clear-reward</x:v>
+      </x:c>
+      <x:c r="AM323"/>
+      <x:c r="AN323"/>
+      <x:c r="AO323"/>
+      <x:c r="AP323"/>
+      <x:c r="AQ323"/>
+      <x:c r="AR323" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS323"/>
+      <x:c r="AT323"/>
+      <x:c r="AU323"/>
+      <x:c r="AV323"/>
+      <x:c r="AW323"/>
+      <x:c r="AX323"/>
+      <x:c r="AY323" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ323" t="str">
+        <x:v>mist-gate</x:v>
+      </x:c>
+      <x:c r="BA323" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB323"/>
+      <x:c r="BC323" t="str">
+        <x:v>{"mist_ore":6,"mist_herb":6}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec7fcc6907244f8"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2f7ce9c34d249be"/>
 </x:worksheet>
 </file>
 
@@ -50623,9 +50857,105 @@
       <x:c r="AC393"/>
       <x:c r="AD393"/>
     </x:row>
+    <x:row r="394">
+      <x:c r="A394" t="str">
+        <x:v>hub-gate-reward-wind</x:v>
+      </x:c>
+      <x:c r="B394" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>hub-node:wind-gate</x:v>
+      </x:c>
+      <x:c r="E394"/>
+      <x:c r="F394" t="str">
+        <x:v>击退登港先锋首通奖励</x:v>
+      </x:c>
+      <x:c r="G394"/>
+      <x:c r="H394" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I394" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J394"/>
+      <x:c r="K394"/>
+      <x:c r="L394"/>
+      <x:c r="M394"/>
+      <x:c r="N394"/>
+      <x:c r="O394"/>
+      <x:c r="P394"/>
+      <x:c r="Q394"/>
+      <x:c r="R394"/>
+      <x:c r="S394"/>
+      <x:c r="T394"/>
+      <x:c r="U394"/>
+      <x:c r="V394"/>
+      <x:c r="W394"/>
+      <x:c r="X394"/>
+      <x:c r="Y394" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z394"/>
+      <x:c r="AA394"/>
+      <x:c r="AB394"/>
+      <x:c r="AC394"/>
+      <x:c r="AD394"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" t="str">
+        <x:v>hub-gate-reward-mist</x:v>
+      </x:c>
+      <x:c r="B395" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>hub_fact</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>hub-node:mist-gate</x:v>
+      </x:c>
+      <x:c r="E395"/>
+      <x:c r="F395" t="str">
+        <x:v>截击军需官首通奖励</x:v>
+      </x:c>
+      <x:c r="G395"/>
+      <x:c r="H395" t="str">
+        <x:v>ss-map-port</x:v>
+      </x:c>
+      <x:c r="I395" t="str">
+        <x:v>stargate</x:v>
+      </x:c>
+      <x:c r="J395"/>
+      <x:c r="K395"/>
+      <x:c r="L395"/>
+      <x:c r="M395"/>
+      <x:c r="N395"/>
+      <x:c r="O395"/>
+      <x:c r="P395"/>
+      <x:c r="Q395"/>
+      <x:c r="R395"/>
+      <x:c r="S395"/>
+      <x:c r="T395"/>
+      <x:c r="U395"/>
+      <x:c r="V395"/>
+      <x:c r="W395"/>
+      <x:c r="X395"/>
+      <x:c r="Y395" s="14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z395"/>
+      <x:c r="AA395"/>
+      <x:c r="AB395"/>
+      <x:c r="AC395"/>
+      <x:c r="AD395"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51087d28e87043e9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26aa3475b07b4d4f"/>
 </x:worksheet>
 </file>
 
@@ -51691,7 +52021,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R745f11af0cc44127"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9386d05a02f5473b"/>
 </x:worksheet>
 </file>
 
@@ -69278,7 +69608,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e6ec6deeea24a1f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d39cf7fae2d4c39"/>
 </x:worksheet>
 </file>
 
@@ -70074,7 +70404,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ccd1f50e5744c5e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25c1ad360fda4200"/>
 </x:worksheet>
 </file>
 
@@ -70975,6 +71305,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8463ef2ba35746cd"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c67c728aa0141e9"/>
 </x:worksheet>
 </file>